--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="224">
   <si>
     <t>Date</t>
   </si>
@@ -202,6 +202,9 @@
     <t>07:00</t>
   </si>
   <si>
+    <t>08:00</t>
+  </si>
+  <si>
     <t>09:00</t>
   </si>
   <si>
@@ -262,6 +265,9 @@
     <t>Russia Russian Premier League</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
     <t>Indonesia Liga 1</t>
   </si>
   <si>
@@ -274,42 +280,48 @@
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Spain Primera Division Women</t>
+  </si>
+  <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Spain Primera Division Women</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
@@ -319,15 +331,15 @@
     <t>Italy Serie A</t>
   </si>
   <si>
+    <t>Spain La Liga</t>
+  </si>
+  <si>
     <t>England Premier League</t>
   </si>
   <si>
     <t>Bolivia LFPB</t>
   </si>
   <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
@@ -337,6 +349,9 @@
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>2025/2026</t>
   </si>
   <si>
@@ -346,15 +361,21 @@
     <t>Akron</t>
   </si>
   <si>
+    <t>Yenisey</t>
+  </si>
+  <si>
+    <t>Ural</t>
+  </si>
+  <si>
+    <t>Bhayangkara</t>
+  </si>
+  <si>
+    <t>Ethiopian Medhin</t>
+  </si>
+  <si>
     <t>Bali United</t>
   </si>
   <si>
-    <t>Ethiopian Medhin</t>
-  </si>
-  <si>
-    <t>Bhayangkara</t>
-  </si>
-  <si>
     <t>Olimpiyets</t>
   </si>
   <si>
@@ -364,33 +385,45 @@
     <t>East Bengal</t>
   </si>
   <si>
+    <t>Shinnik</t>
+  </si>
+  <si>
     <t>Al Nasr</t>
   </si>
   <si>
     <t>Spartak Moskva</t>
   </si>
   <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Semendrija 1924</t>
+  </si>
+  <si>
+    <t>Dinamo Jug</t>
+  </si>
+  <si>
+    <t>Spaeri</t>
+  </si>
+  <si>
     <t>Grobiņa</t>
   </si>
   <si>
-    <t>Opava</t>
-  </si>
-  <si>
     <t>Metaloglobus</t>
   </si>
   <si>
+    <t>Olympic Safi</t>
+  </si>
+  <si>
     <t>Malmö FF W</t>
   </si>
   <si>
-    <t>Olympic Safi</t>
+    <t>Odra Opole</t>
   </si>
   <si>
     <t>Śląsk Wrocław</t>
   </si>
   <si>
-    <t>Odra Opole</t>
-  </si>
-  <si>
     <t>Al Jazira</t>
   </si>
   <si>
@@ -400,25 +433,31 @@
     <t>Neom SC</t>
   </si>
   <si>
+    <t>Madrid CFF</t>
+  </si>
+  <si>
+    <t>Dinamo Moskva</t>
+  </si>
+  <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
+    <t>Rustavi</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Randers</t>
+  </si>
+  <si>
     <t>Sirius</t>
   </si>
   <si>
-    <t>Madrid CFF</t>
-  </si>
-  <si>
     <t>Cracovia Kraków</t>
   </si>
   <si>
-    <t>Dinamo Moskva</t>
-  </si>
-  <si>
-    <t>Randers</t>
-  </si>
-  <si>
-    <t>Super Nova</t>
-  </si>
-  <si>
-    <t>Egersund</t>
+    <t>Al Taawon</t>
   </si>
   <si>
     <t>FCSB</t>
@@ -427,72 +466,78 @@
     <t>Yacoub El Mansour</t>
   </si>
   <si>
-    <t>Al Taawon</t>
+    <t>Stade Nyonnais</t>
+  </si>
+  <si>
+    <t>Neuchâtel Xamax</t>
+  </si>
+  <si>
+    <t>Vaduz</t>
   </si>
   <si>
     <t>Bellinzona</t>
   </si>
   <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
-    <t>Stade Nyonnais</t>
-  </si>
-  <si>
     <t>Yverdon Sport</t>
   </si>
   <si>
-    <t>Neuchâtel Xamax</t>
-  </si>
-  <si>
     <t>SD Huesca</t>
   </si>
   <si>
     <t>Napoli</t>
   </si>
   <si>
+    <t>Rayo Vallecano</t>
+  </si>
+  <si>
     <t>Tottenham Hotspur</t>
   </si>
   <si>
     <t>ABB</t>
   </si>
   <si>
-    <t>Rayo Vallecano</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>Mushuc Runa SC</t>
+  </si>
+  <si>
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>Maccabi Tel Aviv</t>
-  </si>
-  <si>
-    <t>Mushuc Runa SC</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
+    <t>Curicó Unido</t>
   </si>
   <si>
     <t>Rostov</t>
   </si>
   <si>
+    <t>Arsenal Tula</t>
+  </si>
+  <si>
+    <t>KAMAZ</t>
+  </si>
+  <si>
+    <t>Madura United</t>
+  </si>
+  <si>
+    <t>Ethiopia Nigd Bank</t>
+  </si>
+  <si>
     <t>Borneo</t>
   </si>
   <si>
-    <t>Ethiopia Nigd Bank</t>
-  </si>
-  <si>
-    <t>Madura United</t>
-  </si>
-  <si>
     <t>CSKA Moskva</t>
   </si>
   <si>
@@ -502,33 +547,45 @@
     <t>Minerva Punjab</t>
   </si>
   <si>
+    <t>Torpedo Moskva</t>
+  </si>
+  <si>
     <t>Al Ittihad Kalba</t>
   </si>
   <si>
     <t>Rubin Kazan</t>
   </si>
   <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
+    <t>Borac Čačak</t>
+  </si>
+  <si>
+    <t>Tekstilac Odžaci</t>
+  </si>
+  <si>
+    <t>Gagra</t>
+  </si>
+  <si>
     <t>FS Jelgava</t>
   </si>
   <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
     <t>Hermannstadt</t>
   </si>
   <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
     <t>Häcken W</t>
   </si>
   <si>
-    <t>FUS Rabat</t>
+    <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
     <t>ŁKS Łódź</t>
   </si>
   <si>
-    <t>Pogoń Grod. Mazowiecki</t>
-  </si>
-  <si>
     <t>Al Wasl</t>
   </si>
   <si>
@@ -538,25 +595,31 @@
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>Sevilla W</t>
+  </si>
+  <si>
+    <t>Krasnodar</t>
+  </si>
+  <si>
+    <t>Tukums</t>
+  </si>
+  <si>
+    <t>Dinamo Tbilisi</t>
+  </si>
+  <si>
+    <t>Odd</t>
+  </si>
+  <si>
+    <t>OB</t>
+  </si>
+  <si>
     <t>Örgryte</t>
   </si>
   <si>
-    <t>Sevilla W</t>
-  </si>
-  <si>
     <t>Radomiak Radom</t>
   </si>
   <si>
-    <t>Krasnodar</t>
-  </si>
-  <si>
-    <t>OB</t>
-  </si>
-  <si>
-    <t>Tukums</t>
-  </si>
-  <si>
-    <t>Odd</t>
+    <t>Al Ahli</t>
   </si>
   <si>
     <t>Unirea Slobozia</t>
@@ -565,58 +628,58 @@
     <t>Kawkab Marrakech</t>
   </si>
   <si>
-    <t>Al Ahli</t>
+    <t>Stade Lausanne-Ouchy</t>
+  </si>
+  <si>
+    <t>Étoile Carouge</t>
+  </si>
+  <si>
+    <t>Aarau</t>
   </si>
   <si>
     <t>Wil</t>
   </si>
   <si>
-    <t>Aarau</t>
-  </si>
-  <si>
-    <t>Stade Lausanne-Ouchy</t>
-  </si>
-  <si>
     <t>Rapperswil-Jona</t>
   </si>
   <si>
-    <t>Étoile Carouge</t>
-  </si>
-  <si>
     <t>Real Sociedad II</t>
   </si>
   <si>
     <t>Bologna</t>
   </si>
   <si>
+    <t>Girona FC</t>
+  </si>
+  <si>
     <t>Leeds United</t>
   </si>
   <si>
     <t>Oriente Petrolero</t>
   </si>
   <si>
-    <t>Girona FC</t>
-  </si>
-  <si>
     <t>Olympique Dcheïra</t>
   </si>
   <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>LDU Quito</t>
+  </si>
+  <si>
     <t>Hapoel Petah Tikva</t>
   </si>
   <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>LDU Quito</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
+    <t>San Marcos</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -986,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI47"/>
+  <dimension ref="A1:BI55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:61">
@@ -1182,16 +1245,16 @@
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F2" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1218,7 +1281,7 @@
         <v>-1</v>
       </c>
       <c r="O2" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P2">
         <v>2.72</v>
@@ -1364,19 +1427,19 @@
         <v>46153</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F3" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1403,7 +1466,7 @@
         <v>-1</v>
       </c>
       <c r="O3" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -1541,7 +1604,7 @@
         <v>0</v>
       </c>
       <c r="BI3" s="3">
-        <v>46153.375</v>
+        <v>46153.29166666666</v>
       </c>
     </row>
     <row r="4" spans="1:61">
@@ -1555,13 +1618,13 @@
         <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F4" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1588,7 +1651,7 @@
         <v>-1</v>
       </c>
       <c r="O4" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1726,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="BI4" s="3">
-        <v>46153.375</v>
+        <v>46153.33333333334</v>
       </c>
     </row>
     <row r="5" spans="1:61">
@@ -1734,19 +1797,19 @@
         <v>46153</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F5" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1773,7 +1836,7 @@
         <v>-1</v>
       </c>
       <c r="O5" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1922,16 +1985,16 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F6" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1958,16 +2021,16 @@
         <v>-1</v>
       </c>
       <c r="O6" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P6">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -2096,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="BI6" s="3">
-        <v>46153.38541666666</v>
+        <v>46153.375</v>
       </c>
     </row>
     <row r="7" spans="1:61">
@@ -2104,19 +2167,19 @@
         <v>46153</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F7" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2143,7 +2206,7 @@
         <v>-1</v>
       </c>
       <c r="O7" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -2281,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3">
-        <v>46153.41666666666</v>
+        <v>46153.375</v>
       </c>
     </row>
     <row r="8" spans="1:61">
@@ -2289,19 +2352,19 @@
         <v>46153</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F8" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2328,16 +2391,16 @@
         <v>-1</v>
       </c>
       <c r="O8" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -2466,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="BI8" s="3">
-        <v>46153.45833333334</v>
+        <v>46153.38541666666</v>
       </c>
     </row>
     <row r="9" spans="1:61">
@@ -2474,19 +2537,19 @@
         <v>46153</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
         <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F9" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2513,7 +2576,7 @@
         <v>-1</v>
       </c>
       <c r="O9" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -2651,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3">
-        <v>46153.46527777778</v>
+        <v>46153.41666666666</v>
       </c>
     </row>
     <row r="10" spans="1:61">
@@ -2659,19 +2722,19 @@
         <v>46153</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F10" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2698,16 +2761,16 @@
         <v>-1</v>
       </c>
       <c r="O10" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P10">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>5.49</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -2836,7 +2899,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3">
-        <v>46153.47916666666</v>
+        <v>46153.45833333334</v>
       </c>
     </row>
     <row r="11" spans="1:61">
@@ -2844,19 +2907,19 @@
         <v>46153</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F11" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2883,7 +2946,7 @@
         <v>-1</v>
       </c>
       <c r="O11" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -3021,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3">
-        <v>46153.5</v>
+        <v>46153.45833333334</v>
       </c>
     </row>
     <row r="12" spans="1:61">
@@ -3029,19 +3092,19 @@
         <v>46153</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
         <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F12" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3068,7 +3131,7 @@
         <v>-1</v>
       </c>
       <c r="O12" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -3206,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3">
-        <v>46153.5</v>
+        <v>46153.46527777778</v>
       </c>
     </row>
     <row r="13" spans="1:61">
@@ -3217,16 +3280,16 @@
         <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F13" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -3253,16 +3316,16 @@
         <v>-1</v>
       </c>
       <c r="O13" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -3391,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3">
-        <v>46153.5</v>
+        <v>46153.47916666666</v>
       </c>
     </row>
     <row r="14" spans="1:61">
@@ -3402,16 +3465,16 @@
         <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F14" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3438,7 +3501,7 @@
         <v>-1</v>
       </c>
       <c r="O14" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -3576,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3">
-        <v>46153.54166666666</v>
+        <v>46153.5</v>
       </c>
     </row>
     <row r="15" spans="1:61">
@@ -3587,16 +3650,16 @@
         <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F15" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3623,7 +3686,7 @@
         <v>-1</v>
       </c>
       <c r="O15" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -3761,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3">
-        <v>46153.54166666666</v>
+        <v>46153.5</v>
       </c>
     </row>
     <row r="16" spans="1:61">
@@ -3769,19 +3832,19 @@
         <v>46153</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E16" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F16" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3808,7 +3871,7 @@
         <v>-1</v>
       </c>
       <c r="O16" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -3946,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3">
-        <v>46153.5625</v>
+        <v>46153.5</v>
       </c>
     </row>
     <row r="17" spans="1:61">
@@ -3954,19 +4017,19 @@
         <v>46153</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E17" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F17" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3993,7 +4056,7 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -4131,7 +4194,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3">
-        <v>46153.5625</v>
+        <v>46153.5</v>
       </c>
     </row>
     <row r="18" spans="1:61">
@@ -4139,19 +4202,19 @@
         <v>46153</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E18" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F18" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -4178,7 +4241,7 @@
         <v>-1</v>
       </c>
       <c r="O18" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -4316,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3">
-        <v>46153.57291666666</v>
+        <v>46153.5</v>
       </c>
     </row>
     <row r="19" spans="1:61">
@@ -4324,19 +4387,19 @@
         <v>46153</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E19" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F19" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -4363,16 +4426,16 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -4501,7 +4564,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3">
-        <v>46153.57291666666</v>
+        <v>46153.5</v>
       </c>
     </row>
     <row r="20" spans="1:61">
@@ -4509,19 +4572,19 @@
         <v>46153</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E20" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F20" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4548,7 +4611,7 @@
         <v>-1</v>
       </c>
       <c r="O20" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -4686,7 +4749,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3">
-        <v>46153.57638888889</v>
+        <v>46153.54166666666</v>
       </c>
     </row>
     <row r="21" spans="1:61">
@@ -4694,19 +4757,19 @@
         <v>46153</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E21" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F21" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4733,7 +4796,7 @@
         <v>-1</v>
       </c>
       <c r="O21" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -4871,7 +4934,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3">
-        <v>46153.58333333334</v>
+        <v>46153.54166666666</v>
       </c>
     </row>
     <row r="22" spans="1:61">
@@ -4879,19 +4942,19 @@
         <v>46153</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E22" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F22" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4918,7 +4981,7 @@
         <v>-1</v>
       </c>
       <c r="O22" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -5056,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3">
-        <v>46153.58333333334</v>
+        <v>46153.5625</v>
       </c>
     </row>
     <row r="23" spans="1:61">
@@ -5064,19 +5127,19 @@
         <v>46153</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s">
         <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E23" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F23" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -5103,7 +5166,7 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -5241,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3">
-        <v>46153.58333333334</v>
+        <v>46153.5625</v>
       </c>
     </row>
     <row r="24" spans="1:61">
@@ -5249,19 +5312,19 @@
         <v>46153</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E24" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F24" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -5288,16 +5351,16 @@
         <v>-1</v>
       </c>
       <c r="O24" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P24">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -5426,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3">
-        <v>46153.58333333334</v>
+        <v>46153.57291666666</v>
       </c>
     </row>
     <row r="25" spans="1:61">
@@ -5434,19 +5497,19 @@
         <v>46153</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E25" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F25" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -5473,16 +5536,16 @@
         <v>-1</v>
       </c>
       <c r="O25" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P25">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -5611,7 +5674,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3">
-        <v>46153.58333333334</v>
+        <v>46153.57291666666</v>
       </c>
     </row>
     <row r="26" spans="1:61">
@@ -5622,16 +5685,16 @@
         <v>73</v>
       </c>
       <c r="C26" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E26" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F26" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5658,7 +5721,7 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5796,7 +5859,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3">
-        <v>46153.58333333334</v>
+        <v>46153.57638888889</v>
       </c>
     </row>
     <row r="27" spans="1:61">
@@ -5804,19 +5867,19 @@
         <v>46153</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
         <v>97</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E27" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F27" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5843,16 +5906,16 @@
         <v>-1</v>
       </c>
       <c r="O27" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P27">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -5992,16 +6055,16 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D28" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E28" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F28" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6028,16 +6091,16 @@
         <v>-1</v>
       </c>
       <c r="O28" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -6166,7 +6229,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3">
-        <v>46153.625</v>
+        <v>46153.58333333334</v>
       </c>
     </row>
     <row r="29" spans="1:61">
@@ -6177,16 +6240,16 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E29" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F29" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6213,7 +6276,7 @@
         <v>-1</v>
       </c>
       <c r="O29" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -6351,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3">
-        <v>46153.625</v>
+        <v>46153.58333333334</v>
       </c>
     </row>
     <row r="30" spans="1:61">
@@ -6362,16 +6425,16 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D30" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E30" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F30" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6398,7 +6461,7 @@
         <v>-1</v>
       </c>
       <c r="O30" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -6536,7 +6599,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3">
-        <v>46153.625</v>
+        <v>46153.58333333334</v>
       </c>
     </row>
     <row r="31" spans="1:61">
@@ -6544,19 +6607,19 @@
         <v>46153</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C31" t="s">
         <v>98</v>
       </c>
       <c r="D31" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F31" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -6583,16 +6646,16 @@
         <v>-1</v>
       </c>
       <c r="O31" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -6721,7 +6784,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3">
-        <v>46153.63541666666</v>
+        <v>46153.58333333334</v>
       </c>
     </row>
     <row r="32" spans="1:61">
@@ -6729,19 +6792,19 @@
         <v>46153</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E32" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="F32" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -6768,16 +6831,16 @@
         <v>-1</v>
       </c>
       <c r="O32" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -6906,7 +6969,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3">
-        <v>46153.63541666666</v>
+        <v>46153.58333333334</v>
       </c>
     </row>
     <row r="33" spans="1:61">
@@ -6914,19 +6977,19 @@
         <v>46153</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D33" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E33" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F33" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -6953,7 +7016,7 @@
         <v>-1</v>
       </c>
       <c r="O33" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -7091,7 +7154,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3">
-        <v>46153.63541666666</v>
+        <v>46153.58333333334</v>
       </c>
     </row>
     <row r="34" spans="1:61">
@@ -7099,19 +7162,19 @@
         <v>46153</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D34" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E34" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F34" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -7138,7 +7201,7 @@
         <v>-1</v>
       </c>
       <c r="O34" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -7276,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3">
-        <v>46153.63541666666</v>
+        <v>46153.58333333334</v>
       </c>
     </row>
     <row r="35" spans="1:61">
@@ -7287,16 +7350,16 @@
         <v>75</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E35" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F35" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -7323,7 +7386,7 @@
         <v>-1</v>
       </c>
       <c r="O35" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -7461,7 +7524,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3">
-        <v>46153.63541666666</v>
+        <v>46153.625</v>
       </c>
     </row>
     <row r="36" spans="1:61">
@@ -7469,19 +7532,19 @@
         <v>46153</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D36" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E36" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F36" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -7508,16 +7571,16 @@
         <v>-1</v>
       </c>
       <c r="O36" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7646,7 +7709,7 @@
         <v>0</v>
       </c>
       <c r="BI36" s="3">
-        <v>46153.64583333334</v>
+        <v>46153.625</v>
       </c>
     </row>
     <row r="37" spans="1:61">
@@ -7654,19 +7717,19 @@
         <v>46153</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D37" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E37" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F37" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -7693,16 +7756,16 @@
         <v>-1</v>
       </c>
       <c r="O37" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P37">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>6.24</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -7741,10 +7804,10 @@
         <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG37">
         <v>0</v>
@@ -7831,7 +7894,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3">
-        <v>46153.65625</v>
+        <v>46153.625</v>
       </c>
     </row>
     <row r="38" spans="1:61">
@@ -7839,19 +7902,19 @@
         <v>46153</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D38" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E38" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F38" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -7878,16 +7941,16 @@
         <v>-1</v>
       </c>
       <c r="O38" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P38">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8016,7 +8079,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3">
-        <v>46153.66666666666</v>
+        <v>46153.63541666666</v>
       </c>
     </row>
     <row r="39" spans="1:61">
@@ -8024,19 +8087,19 @@
         <v>46153</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C39" t="s">
         <v>102</v>
       </c>
       <c r="D39" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E39" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F39" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -8063,7 +8126,7 @@
         <v>-1</v>
       </c>
       <c r="O39" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -8201,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3">
-        <v>46153.66666666666</v>
+        <v>46153.63541666666</v>
       </c>
     </row>
     <row r="40" spans="1:61">
@@ -8209,19 +8272,19 @@
         <v>46153</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C40" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D40" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E40" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="F40" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -8248,7 +8311,7 @@
         <v>-1</v>
       </c>
       <c r="O40" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -8386,7 +8449,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3">
-        <v>46153.66666666666</v>
+        <v>46153.63541666666</v>
       </c>
     </row>
     <row r="41" spans="1:61">
@@ -8394,19 +8457,19 @@
         <v>46153</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C41" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D41" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E41" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="F41" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -8433,7 +8496,7 @@
         <v>-1</v>
       </c>
       <c r="O41" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -8571,7 +8634,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3">
-        <v>46153.70833333334</v>
+        <v>46153.63541666666</v>
       </c>
     </row>
     <row r="42" spans="1:61">
@@ -8579,19 +8642,19 @@
         <v>46153</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E42" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="F42" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -8618,7 +8681,7 @@
         <v>-1</v>
       </c>
       <c r="O42" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P42">
         <v>0</v>
@@ -8756,7 +8819,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3">
-        <v>46153.875</v>
+        <v>46153.63541666666</v>
       </c>
     </row>
     <row r="43" spans="1:61">
@@ -8764,19 +8827,19 @@
         <v>46153</v>
       </c>
       <c r="B43" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C43" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D43" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E43" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F43" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -8803,7 +8866,7 @@
         <v>-1</v>
       </c>
       <c r="O43" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="P43">
         <v>0</v>
@@ -8941,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3">
-        <v>46153.875</v>
+        <v>46153.64583333334</v>
       </c>
     </row>
     <row r="44" spans="1:61">
@@ -8949,19 +9012,19 @@
         <v>46153</v>
       </c>
       <c r="B44" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C44" t="s">
         <v>104</v>
       </c>
       <c r="D44" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E44" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="F44" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -8988,16 +9051,16 @@
         <v>-1</v>
       </c>
       <c r="O44" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9036,10 +9099,10 @@
         <v>0</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG44">
         <v>0</v>
@@ -9126,7 +9189,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3">
-        <v>46153.875</v>
+        <v>46153.65625</v>
       </c>
     </row>
     <row r="45" spans="1:61">
@@ -9134,19 +9197,19 @@
         <v>46153</v>
       </c>
       <c r="B45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C45" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D45" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E45" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F45" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -9173,7 +9236,7 @@
         <v>-1</v>
       </c>
       <c r="O45" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P45">
         <v>0</v>
@@ -9311,7 +9374,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3">
-        <v>46153.875</v>
+        <v>46153.66666666666</v>
       </c>
     </row>
     <row r="46" spans="1:61">
@@ -9319,19 +9382,19 @@
         <v>46153</v>
       </c>
       <c r="B46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C46" t="s">
         <v>106</v>
       </c>
       <c r="D46" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E46" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F46" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -9358,16 +9421,16 @@
         <v>-1</v>
       </c>
       <c r="O46" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P46">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q46">
-        <v>3.2</v>
+        <v>3.84</v>
       </c>
       <c r="R46">
-        <v>2.3</v>
+        <v>3.58</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -9496,7 +9559,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3">
-        <v>46153.875</v>
+        <v>46153.66666666666</v>
       </c>
     </row>
     <row r="47" spans="1:61">
@@ -9504,19 +9567,19 @@
         <v>46153</v>
       </c>
       <c r="B47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C47" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D47" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E47" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F47" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -9543,7 +9606,7 @@
         <v>-1</v>
       </c>
       <c r="O47" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="P47">
         <v>0</v>
@@ -9681,6 +9744,1486 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3">
+        <v>46153.66666666666</v>
+      </c>
+    </row>
+    <row r="48" spans="1:61">
+      <c r="A48" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B48" t="s">
+        <v>80</v>
+      </c>
+      <c r="C48" t="s">
+        <v>93</v>
+      </c>
+      <c r="D48" t="s">
+        <v>112</v>
+      </c>
+      <c r="E48" t="s">
+        <v>160</v>
+      </c>
+      <c r="F48" t="s">
+        <v>214</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>-1</v>
+      </c>
+      <c r="N48">
+        <v>-1</v>
+      </c>
+      <c r="O48" t="s">
+        <v>222</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
+        <v>0</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>0</v>
+      </c>
+      <c r="AG48">
+        <v>0</v>
+      </c>
+      <c r="AH48">
+        <v>0</v>
+      </c>
+      <c r="AI48">
+        <v>0</v>
+      </c>
+      <c r="AJ48">
+        <v>0</v>
+      </c>
+      <c r="AK48">
+        <v>0</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>0</v>
+      </c>
+      <c r="AN48">
+        <v>0</v>
+      </c>
+      <c r="AO48">
+        <v>0</v>
+      </c>
+      <c r="AP48">
+        <v>0</v>
+      </c>
+      <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48">
+        <v>0</v>
+      </c>
+      <c r="AV48">
+        <v>0</v>
+      </c>
+      <c r="AW48">
+        <v>0</v>
+      </c>
+      <c r="AX48">
+        <v>0</v>
+      </c>
+      <c r="AY48">
+        <v>0</v>
+      </c>
+      <c r="AZ48">
+        <v>0</v>
+      </c>
+      <c r="BA48">
+        <v>0</v>
+      </c>
+      <c r="BB48">
+        <v>0</v>
+      </c>
+      <c r="BC48">
+        <v>0</v>
+      </c>
+      <c r="BD48">
+        <v>0</v>
+      </c>
+      <c r="BE48">
+        <v>0</v>
+      </c>
+      <c r="BF48">
+        <v>0</v>
+      </c>
+      <c r="BG48">
+        <v>0</v>
+      </c>
+      <c r="BH48">
+        <v>0</v>
+      </c>
+      <c r="BI48" s="3">
+        <v>46153.70833333334</v>
+      </c>
+    </row>
+    <row r="49" spans="1:61">
+      <c r="A49" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B49" t="s">
+        <v>81</v>
+      </c>
+      <c r="C49" t="s">
+        <v>108</v>
+      </c>
+      <c r="D49" t="s">
+        <v>112</v>
+      </c>
+      <c r="E49" t="s">
+        <v>161</v>
+      </c>
+      <c r="F49" t="s">
+        <v>215</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>-1</v>
+      </c>
+      <c r="N49">
+        <v>-1</v>
+      </c>
+      <c r="O49" t="s">
+        <v>222</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49">
+        <v>0</v>
+      </c>
+      <c r="AI49">
+        <v>0</v>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>0</v>
+      </c>
+      <c r="AN49">
+        <v>0</v>
+      </c>
+      <c r="AO49">
+        <v>0</v>
+      </c>
+      <c r="AP49">
+        <v>0</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49">
+        <v>0</v>
+      </c>
+      <c r="AV49">
+        <v>0</v>
+      </c>
+      <c r="AW49">
+        <v>0</v>
+      </c>
+      <c r="AX49">
+        <v>0</v>
+      </c>
+      <c r="AY49">
+        <v>0</v>
+      </c>
+      <c r="AZ49">
+        <v>0</v>
+      </c>
+      <c r="BA49">
+        <v>0</v>
+      </c>
+      <c r="BB49">
+        <v>0</v>
+      </c>
+      <c r="BC49">
+        <v>0</v>
+      </c>
+      <c r="BD49">
+        <v>0</v>
+      </c>
+      <c r="BE49">
+        <v>0</v>
+      </c>
+      <c r="BF49">
+        <v>0</v>
+      </c>
+      <c r="BG49">
+        <v>0</v>
+      </c>
+      <c r="BH49">
+        <v>0</v>
+      </c>
+      <c r="BI49" s="3">
+        <v>46153.875</v>
+      </c>
+    </row>
+    <row r="50" spans="1:61">
+      <c r="A50" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B50" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" t="s">
+        <v>109</v>
+      </c>
+      <c r="D50" t="s">
+        <v>112</v>
+      </c>
+      <c r="E50" t="s">
+        <v>162</v>
+      </c>
+      <c r="F50" t="s">
+        <v>216</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>-1</v>
+      </c>
+      <c r="N50">
+        <v>-1</v>
+      </c>
+      <c r="O50" t="s">
+        <v>222</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <v>0</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
+        <v>0</v>
+      </c>
+      <c r="AH50">
+        <v>0</v>
+      </c>
+      <c r="AI50">
+        <v>0</v>
+      </c>
+      <c r="AJ50">
+        <v>0</v>
+      </c>
+      <c r="AK50">
+        <v>0</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>0</v>
+      </c>
+      <c r="AN50">
+        <v>0</v>
+      </c>
+      <c r="AO50">
+        <v>0</v>
+      </c>
+      <c r="AP50">
+        <v>0</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50">
+        <v>0</v>
+      </c>
+      <c r="AV50">
+        <v>0</v>
+      </c>
+      <c r="AW50">
+        <v>0</v>
+      </c>
+      <c r="AX50">
+        <v>0</v>
+      </c>
+      <c r="AY50">
+        <v>0</v>
+      </c>
+      <c r="AZ50">
+        <v>0</v>
+      </c>
+      <c r="BA50">
+        <v>0</v>
+      </c>
+      <c r="BB50">
+        <v>0</v>
+      </c>
+      <c r="BC50">
+        <v>0</v>
+      </c>
+      <c r="BD50">
+        <v>0</v>
+      </c>
+      <c r="BE50">
+        <v>0</v>
+      </c>
+      <c r="BF50">
+        <v>0</v>
+      </c>
+      <c r="BG50">
+        <v>0</v>
+      </c>
+      <c r="BH50">
+        <v>0</v>
+      </c>
+      <c r="BI50" s="3">
+        <v>46153.875</v>
+      </c>
+    </row>
+    <row r="51" spans="1:61">
+      <c r="A51" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B51" t="s">
+        <v>81</v>
+      </c>
+      <c r="C51" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" t="s">
+        <v>112</v>
+      </c>
+      <c r="E51" t="s">
+        <v>163</v>
+      </c>
+      <c r="F51" t="s">
+        <v>217</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>-1</v>
+      </c>
+      <c r="N51">
+        <v>-1</v>
+      </c>
+      <c r="O51" t="s">
+        <v>222</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51">
+        <v>0</v>
+      </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>0</v>
+      </c>
+      <c r="AG51">
+        <v>0</v>
+      </c>
+      <c r="AH51">
+        <v>0</v>
+      </c>
+      <c r="AI51">
+        <v>0</v>
+      </c>
+      <c r="AJ51">
+        <v>0</v>
+      </c>
+      <c r="AK51">
+        <v>0</v>
+      </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
+      <c r="AM51">
+        <v>0</v>
+      </c>
+      <c r="AN51">
+        <v>0</v>
+      </c>
+      <c r="AO51">
+        <v>0</v>
+      </c>
+      <c r="AP51">
+        <v>0</v>
+      </c>
+      <c r="AQ51">
+        <v>0</v>
+      </c>
+      <c r="AR51">
+        <v>0</v>
+      </c>
+      <c r="AS51">
+        <v>0</v>
+      </c>
+      <c r="AT51">
+        <v>0</v>
+      </c>
+      <c r="AU51">
+        <v>0</v>
+      </c>
+      <c r="AV51">
+        <v>0</v>
+      </c>
+      <c r="AW51">
+        <v>0</v>
+      </c>
+      <c r="AX51">
+        <v>0</v>
+      </c>
+      <c r="AY51">
+        <v>0</v>
+      </c>
+      <c r="AZ51">
+        <v>0</v>
+      </c>
+      <c r="BA51">
+        <v>0</v>
+      </c>
+      <c r="BB51">
+        <v>0</v>
+      </c>
+      <c r="BC51">
+        <v>0</v>
+      </c>
+      <c r="BD51">
+        <v>0</v>
+      </c>
+      <c r="BE51">
+        <v>0</v>
+      </c>
+      <c r="BF51">
+        <v>0</v>
+      </c>
+      <c r="BG51">
+        <v>0</v>
+      </c>
+      <c r="BH51">
+        <v>0</v>
+      </c>
+      <c r="BI51" s="3">
+        <v>46153.875</v>
+      </c>
+    </row>
+    <row r="52" spans="1:61">
+      <c r="A52" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B52" t="s">
+        <v>81</v>
+      </c>
+      <c r="C52" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" t="s">
+        <v>112</v>
+      </c>
+      <c r="E52" t="s">
+        <v>164</v>
+      </c>
+      <c r="F52" t="s">
+        <v>218</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>-1</v>
+      </c>
+      <c r="N52">
+        <v>-1</v>
+      </c>
+      <c r="O52" t="s">
+        <v>223</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+      <c r="AA52">
+        <v>0</v>
+      </c>
+      <c r="AB52">
+        <v>0</v>
+      </c>
+      <c r="AC52">
+        <v>0</v>
+      </c>
+      <c r="AD52">
+        <v>0</v>
+      </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>0</v>
+      </c>
+      <c r="AG52">
+        <v>0</v>
+      </c>
+      <c r="AH52">
+        <v>0</v>
+      </c>
+      <c r="AI52">
+        <v>0</v>
+      </c>
+      <c r="AJ52">
+        <v>0</v>
+      </c>
+      <c r="AK52">
+        <v>0</v>
+      </c>
+      <c r="AL52">
+        <v>0</v>
+      </c>
+      <c r="AM52">
+        <v>0</v>
+      </c>
+      <c r="AN52">
+        <v>0</v>
+      </c>
+      <c r="AO52">
+        <v>0</v>
+      </c>
+      <c r="AP52">
+        <v>0</v>
+      </c>
+      <c r="AQ52">
+        <v>0</v>
+      </c>
+      <c r="AR52">
+        <v>0</v>
+      </c>
+      <c r="AS52">
+        <v>0</v>
+      </c>
+      <c r="AT52">
+        <v>0</v>
+      </c>
+      <c r="AU52">
+        <v>0</v>
+      </c>
+      <c r="AV52">
+        <v>0</v>
+      </c>
+      <c r="AW52">
+        <v>0</v>
+      </c>
+      <c r="AX52">
+        <v>0</v>
+      </c>
+      <c r="AY52">
+        <v>0</v>
+      </c>
+      <c r="AZ52">
+        <v>0</v>
+      </c>
+      <c r="BA52">
+        <v>0</v>
+      </c>
+      <c r="BB52">
+        <v>0</v>
+      </c>
+      <c r="BC52">
+        <v>0</v>
+      </c>
+      <c r="BD52">
+        <v>0</v>
+      </c>
+      <c r="BE52">
+        <v>0</v>
+      </c>
+      <c r="BF52">
+        <v>0</v>
+      </c>
+      <c r="BG52">
+        <v>0</v>
+      </c>
+      <c r="BH52">
+        <v>0</v>
+      </c>
+      <c r="BI52" s="3">
+        <v>46153.875</v>
+      </c>
+    </row>
+    <row r="53" spans="1:61">
+      <c r="A53" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B53" t="s">
+        <v>81</v>
+      </c>
+      <c r="C53" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" t="s">
+        <v>113</v>
+      </c>
+      <c r="E53" t="s">
+        <v>165</v>
+      </c>
+      <c r="F53" t="s">
+        <v>219</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>-1</v>
+      </c>
+      <c r="N53">
+        <v>-1</v>
+      </c>
+      <c r="O53" t="s">
+        <v>222</v>
+      </c>
+      <c r="P53">
+        <v>2.9</v>
+      </c>
+      <c r="Q53">
+        <v>3.2</v>
+      </c>
+      <c r="R53">
+        <v>2.3</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+      <c r="AA53">
+        <v>0</v>
+      </c>
+      <c r="AB53">
+        <v>0</v>
+      </c>
+      <c r="AC53">
+        <v>0</v>
+      </c>
+      <c r="AD53">
+        <v>0</v>
+      </c>
+      <c r="AE53">
+        <v>0</v>
+      </c>
+      <c r="AF53">
+        <v>0</v>
+      </c>
+      <c r="AG53">
+        <v>0</v>
+      </c>
+      <c r="AH53">
+        <v>0</v>
+      </c>
+      <c r="AI53">
+        <v>0</v>
+      </c>
+      <c r="AJ53">
+        <v>0</v>
+      </c>
+      <c r="AK53">
+        <v>0</v>
+      </c>
+      <c r="AL53">
+        <v>0</v>
+      </c>
+      <c r="AM53">
+        <v>0</v>
+      </c>
+      <c r="AN53">
+        <v>0</v>
+      </c>
+      <c r="AO53">
+        <v>0</v>
+      </c>
+      <c r="AP53">
+        <v>0</v>
+      </c>
+      <c r="AQ53">
+        <v>0</v>
+      </c>
+      <c r="AR53">
+        <v>0</v>
+      </c>
+      <c r="AS53">
+        <v>0</v>
+      </c>
+      <c r="AT53">
+        <v>0</v>
+      </c>
+      <c r="AU53">
+        <v>0</v>
+      </c>
+      <c r="AV53">
+        <v>0</v>
+      </c>
+      <c r="AW53">
+        <v>0</v>
+      </c>
+      <c r="AX53">
+        <v>0</v>
+      </c>
+      <c r="AY53">
+        <v>0</v>
+      </c>
+      <c r="AZ53">
+        <v>0</v>
+      </c>
+      <c r="BA53">
+        <v>0</v>
+      </c>
+      <c r="BB53">
+        <v>0</v>
+      </c>
+      <c r="BC53">
+        <v>0</v>
+      </c>
+      <c r="BD53">
+        <v>0</v>
+      </c>
+      <c r="BE53">
+        <v>0</v>
+      </c>
+      <c r="BF53">
+        <v>0</v>
+      </c>
+      <c r="BG53">
+        <v>0</v>
+      </c>
+      <c r="BH53">
+        <v>0</v>
+      </c>
+      <c r="BI53" s="3">
+        <v>46153.875</v>
+      </c>
+    </row>
+    <row r="54" spans="1:61">
+      <c r="A54" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B54" t="s">
+        <v>81</v>
+      </c>
+      <c r="C54" t="s">
+        <v>108</v>
+      </c>
+      <c r="D54" t="s">
+        <v>112</v>
+      </c>
+      <c r="E54" t="s">
+        <v>166</v>
+      </c>
+      <c r="F54" t="s">
+        <v>220</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>-1</v>
+      </c>
+      <c r="N54">
+        <v>-1</v>
+      </c>
+      <c r="O54" t="s">
+        <v>222</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+      <c r="AA54">
+        <v>0</v>
+      </c>
+      <c r="AB54">
+        <v>0</v>
+      </c>
+      <c r="AC54">
+        <v>0</v>
+      </c>
+      <c r="AD54">
+        <v>0</v>
+      </c>
+      <c r="AE54">
+        <v>0</v>
+      </c>
+      <c r="AF54">
+        <v>0</v>
+      </c>
+      <c r="AG54">
+        <v>0</v>
+      </c>
+      <c r="AH54">
+        <v>0</v>
+      </c>
+      <c r="AI54">
+        <v>0</v>
+      </c>
+      <c r="AJ54">
+        <v>0</v>
+      </c>
+      <c r="AK54">
+        <v>0</v>
+      </c>
+      <c r="AL54">
+        <v>0</v>
+      </c>
+      <c r="AM54">
+        <v>0</v>
+      </c>
+      <c r="AN54">
+        <v>0</v>
+      </c>
+      <c r="AO54">
+        <v>0</v>
+      </c>
+      <c r="AP54">
+        <v>0</v>
+      </c>
+      <c r="AQ54">
+        <v>0</v>
+      </c>
+      <c r="AR54">
+        <v>0</v>
+      </c>
+      <c r="AS54">
+        <v>0</v>
+      </c>
+      <c r="AT54">
+        <v>0</v>
+      </c>
+      <c r="AU54">
+        <v>0</v>
+      </c>
+      <c r="AV54">
+        <v>0</v>
+      </c>
+      <c r="AW54">
+        <v>0</v>
+      </c>
+      <c r="AX54">
+        <v>0</v>
+      </c>
+      <c r="AY54">
+        <v>0</v>
+      </c>
+      <c r="AZ54">
+        <v>0</v>
+      </c>
+      <c r="BA54">
+        <v>0</v>
+      </c>
+      <c r="BB54">
+        <v>0</v>
+      </c>
+      <c r="BC54">
+        <v>0</v>
+      </c>
+      <c r="BD54">
+        <v>0</v>
+      </c>
+      <c r="BE54">
+        <v>0</v>
+      </c>
+      <c r="BF54">
+        <v>0</v>
+      </c>
+      <c r="BG54">
+        <v>0</v>
+      </c>
+      <c r="BH54">
+        <v>0</v>
+      </c>
+      <c r="BI54" s="3">
+        <v>46153.875</v>
+      </c>
+    </row>
+    <row r="55" spans="1:61">
+      <c r="A55" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B55" t="s">
+        <v>81</v>
+      </c>
+      <c r="C55" t="s">
+        <v>111</v>
+      </c>
+      <c r="D55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E55" t="s">
+        <v>167</v>
+      </c>
+      <c r="F55" t="s">
+        <v>221</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>-1</v>
+      </c>
+      <c r="N55">
+        <v>-1</v>
+      </c>
+      <c r="O55" t="s">
+        <v>222</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0</v>
+      </c>
+      <c r="X55">
+        <v>0</v>
+      </c>
+      <c r="Y55">
+        <v>0</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+      <c r="AA55">
+        <v>0</v>
+      </c>
+      <c r="AB55">
+        <v>0</v>
+      </c>
+      <c r="AC55">
+        <v>0</v>
+      </c>
+      <c r="AD55">
+        <v>0</v>
+      </c>
+      <c r="AE55">
+        <v>0</v>
+      </c>
+      <c r="AF55">
+        <v>0</v>
+      </c>
+      <c r="AG55">
+        <v>0</v>
+      </c>
+      <c r="AH55">
+        <v>0</v>
+      </c>
+      <c r="AI55">
+        <v>0</v>
+      </c>
+      <c r="AJ55">
+        <v>0</v>
+      </c>
+      <c r="AK55">
+        <v>0</v>
+      </c>
+      <c r="AL55">
+        <v>0</v>
+      </c>
+      <c r="AM55">
+        <v>0</v>
+      </c>
+      <c r="AN55">
+        <v>0</v>
+      </c>
+      <c r="AO55">
+        <v>0</v>
+      </c>
+      <c r="AP55">
+        <v>0</v>
+      </c>
+      <c r="AQ55">
+        <v>0</v>
+      </c>
+      <c r="AR55">
+        <v>0</v>
+      </c>
+      <c r="AS55">
+        <v>0</v>
+      </c>
+      <c r="AT55">
+        <v>0</v>
+      </c>
+      <c r="AU55">
+        <v>0</v>
+      </c>
+      <c r="AV55">
+        <v>0</v>
+      </c>
+      <c r="AW55">
+        <v>0</v>
+      </c>
+      <c r="AX55">
+        <v>0</v>
+      </c>
+      <c r="AY55">
+        <v>0</v>
+      </c>
+      <c r="AZ55">
+        <v>0</v>
+      </c>
+      <c r="BA55">
+        <v>0</v>
+      </c>
+      <c r="BB55">
+        <v>0</v>
+      </c>
+      <c r="BC55">
+        <v>0</v>
+      </c>
+      <c r="BD55">
+        <v>0</v>
+      </c>
+      <c r="BE55">
+        <v>0</v>
+      </c>
+      <c r="BF55">
+        <v>0</v>
+      </c>
+      <c r="BG55">
+        <v>0</v>
+      </c>
+      <c r="BH55">
+        <v>0</v>
+      </c>
+      <c r="BI55" s="3">
         <v>46153.875</v>
       </c>
     </row>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -262,12 +262,12 @@
     <t>21:00</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
     <t>Russia Russian Premier League</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
     <t>Indonesia Liga 1</t>
   </si>
   <si>
@@ -280,27 +280,27 @@
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
     <t>Romania Liga I</t>
   </si>
   <si>
+    <t>Sweden Damallsvenskan</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Sweden Damallsvenskan</t>
-  </si>
-  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
@@ -310,18 +310,18 @@
     <t>Spain Primera Division Women</t>
   </si>
   <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
@@ -340,6 +340,9 @@
     <t>Bolivia LFPB</t>
   </si>
   <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
@@ -349,33 +352,30 @@
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
-    <t>Chile Primera B</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
     <t>2026</t>
   </si>
   <si>
+    <t>Yenisey</t>
+  </si>
+  <si>
     <t>Akron</t>
   </si>
   <si>
-    <t>Yenisey</t>
-  </si>
-  <si>
     <t>Ural</t>
   </si>
   <si>
     <t>Bhayangkara</t>
   </si>
   <si>
+    <t>Bali United</t>
+  </si>
+  <si>
     <t>Ethiopian Medhin</t>
   </si>
   <si>
-    <t>Bali United</t>
-  </si>
-  <si>
     <t>Olimpiyets</t>
   </si>
   <si>
@@ -394,93 +394,93 @@
     <t>Spartak Moskva</t>
   </si>
   <si>
+    <t>Semendrija 1924</t>
+  </si>
+  <si>
+    <t>Spaeri</t>
+  </si>
+  <si>
     <t>Opava</t>
   </si>
   <si>
-    <t>Semendrija 1924</t>
+    <t>Grobiņa</t>
   </si>
   <si>
     <t>Dinamo Jug</t>
   </si>
   <si>
-    <t>Spaeri</t>
-  </si>
-  <si>
-    <t>Grobiņa</t>
-  </si>
-  <si>
     <t>Metaloglobus</t>
   </si>
   <si>
+    <t>Malmö FF W</t>
+  </si>
+  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
-    <t>Malmö FF W</t>
+    <t>Śląsk Wrocław</t>
   </si>
   <si>
     <t>Odra Opole</t>
   </si>
   <si>
-    <t>Śląsk Wrocław</t>
+    <t>Al Khaleej</t>
   </si>
   <si>
     <t>Al Jazira</t>
   </si>
   <si>
-    <t>Al Khaleej</t>
-  </si>
-  <si>
     <t>Neom SC</t>
   </si>
   <si>
     <t>Madrid CFF</t>
   </si>
   <si>
+    <t>Randers</t>
+  </si>
+  <si>
+    <t>Cracovia Kraków</t>
+  </si>
+  <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
     <t>Dinamo Moskva</t>
   </si>
   <si>
-    <t>Super Nova</t>
+    <t>Sirius</t>
+  </si>
+  <si>
+    <t>Egersund</t>
   </si>
   <si>
     <t>Rustavi</t>
   </si>
   <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Randers</t>
-  </si>
-  <si>
-    <t>Sirius</t>
-  </si>
-  <si>
-    <t>Cracovia Kraków</t>
+    <t>FCSB</t>
   </si>
   <si>
     <t>Al Taawon</t>
   </si>
   <si>
-    <t>FCSB</t>
-  </si>
-  <si>
     <t>Yacoub El Mansour</t>
   </si>
   <si>
+    <t>Vaduz</t>
+  </si>
+  <si>
+    <t>Yverdon Sport</t>
+  </si>
+  <si>
+    <t>Bellinzona</t>
+  </si>
+  <si>
     <t>Stade Nyonnais</t>
   </si>
   <si>
     <t>Neuchâtel Xamax</t>
   </si>
   <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
-    <t>Bellinzona</t>
-  </si>
-  <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
     <t>SD Huesca</t>
   </si>
   <si>
@@ -499,45 +499,45 @@
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
+    <t>Curicó Unido</t>
+  </si>
+  <si>
+    <t>Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
     <t>Beitar Jerusalem</t>
   </si>
   <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>Maccabi Tel Aviv</t>
+    <t>Mushuc Runa SC</t>
   </si>
   <si>
     <t>USM Alger</t>
   </si>
   <si>
-    <t>Mushuc Runa SC</t>
-  </si>
-  <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Curicó Unido</t>
+    <t>Arsenal Tula</t>
   </si>
   <si>
     <t>Rostov</t>
   </si>
   <si>
-    <t>Arsenal Tula</t>
-  </si>
-  <si>
     <t>KAMAZ</t>
   </si>
   <si>
     <t>Madura United</t>
   </si>
   <si>
+    <t>Borneo</t>
+  </si>
+  <si>
     <t>Ethiopia Nigd Bank</t>
   </si>
   <si>
-    <t>Borneo</t>
-  </si>
-  <si>
     <t>CSKA Moskva</t>
   </si>
   <si>
@@ -556,93 +556,93 @@
     <t>Rubin Kazan</t>
   </si>
   <si>
+    <t>Borac Čačak</t>
+  </si>
+  <si>
+    <t>Gagra</t>
+  </si>
+  <si>
     <t>Líšeň</t>
   </si>
   <si>
-    <t>Borac Čačak</t>
+    <t>FS Jelgava</t>
   </si>
   <si>
     <t>Tekstilac Odžaci</t>
   </si>
   <si>
-    <t>Gagra</t>
-  </si>
-  <si>
-    <t>FS Jelgava</t>
-  </si>
-  <si>
     <t>Hermannstadt</t>
   </si>
   <si>
+    <t>Häcken W</t>
+  </si>
+  <si>
     <t>FUS Rabat</t>
   </si>
   <si>
-    <t>Häcken W</t>
+    <t>ŁKS Łódź</t>
   </si>
   <si>
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
-    <t>ŁKS Łódź</t>
+    <t>Al Wahda</t>
   </si>
   <si>
     <t>Al Wasl</t>
   </si>
   <si>
-    <t>Al Wahda</t>
-  </si>
-  <si>
     <t>Al Shabab</t>
   </si>
   <si>
     <t>Sevilla W</t>
   </si>
   <si>
+    <t>OB</t>
+  </si>
+  <si>
+    <t>Radomiak Radom</t>
+  </si>
+  <si>
+    <t>Tukums</t>
+  </si>
+  <si>
     <t>Krasnodar</t>
   </si>
   <si>
-    <t>Tukums</t>
+    <t>Örgryte</t>
+  </si>
+  <si>
+    <t>Odd</t>
   </si>
   <si>
     <t>Dinamo Tbilisi</t>
   </si>
   <si>
-    <t>Odd</t>
-  </si>
-  <si>
-    <t>OB</t>
-  </si>
-  <si>
-    <t>Örgryte</t>
-  </si>
-  <si>
-    <t>Radomiak Radom</t>
+    <t>Unirea Slobozia</t>
   </si>
   <si>
     <t>Al Ahli</t>
   </si>
   <si>
-    <t>Unirea Slobozia</t>
-  </si>
-  <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
+    <t>Aarau</t>
+  </si>
+  <si>
+    <t>Rapperswil-Jona</t>
+  </si>
+  <si>
+    <t>Wil</t>
+  </si>
+  <si>
     <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
     <t>Étoile Carouge</t>
   </si>
   <si>
-    <t>Aarau</t>
-  </si>
-  <si>
-    <t>Wil</t>
-  </si>
-  <si>
-    <t>Rapperswil-Jona</t>
-  </si>
-  <si>
     <t>Real Sociedad II</t>
   </si>
   <si>
@@ -661,25 +661,25 @@
     <t>Olympique Dcheïra</t>
   </si>
   <si>
+    <t>San Marcos</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Hapoel Petah Tikva</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
+    <t>LDU Quito</t>
   </si>
   <si>
     <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>LDU Quito</t>
-  </si>
-  <si>
-    <t>Hapoel Petah Tikva</t>
-  </si>
-  <si>
-    <t>San Marcos</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1284,13 +1284,13 @@
         <v>222</v>
       </c>
       <c r="P2">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -1469,13 +1469,13 @@
         <v>222</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -1615,7 +1615,7 @@
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
         <v>112</v>
@@ -1985,7 +1985,7 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
         <v>112</v>
@@ -2170,7 +2170,7 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
         <v>112</v>
@@ -2355,7 +2355,7 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
         <v>112</v>
@@ -2910,7 +2910,7 @@
         <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
         <v>112</v>
@@ -3280,7 +3280,7 @@
         <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
         <v>112</v>
@@ -3653,7 +3653,7 @@
         <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E15" t="s">
         <v>127</v>
@@ -3835,7 +3835,7 @@
         <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
         <v>112</v>
@@ -4020,7 +4020,7 @@
         <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
         <v>113</v>
@@ -4205,10 +4205,10 @@
         <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E18" t="s">
         <v>130</v>
@@ -4578,7 +4578,7 @@
         <v>93</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E20" t="s">
         <v>132</v>
@@ -4763,7 +4763,7 @@
         <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E21" t="s">
         <v>133</v>
@@ -6055,7 +6055,7 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D28" t="s">
         <v>112</v>
@@ -6094,13 +6094,13 @@
         <v>222</v>
       </c>
       <c r="P28">
-        <v>3.18</v>
+        <v>2.27</v>
       </c>
       <c r="Q28">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="R28">
-        <v>2.33</v>
+        <v>2.87</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -6240,10 +6240,10 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E29" t="s">
         <v>141</v>
@@ -6425,7 +6425,7 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
         <v>113</v>
@@ -6610,10 +6610,10 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E31" t="s">
         <v>143</v>
@@ -6649,13 +6649,13 @@
         <v>222</v>
       </c>
       <c r="P31">
-        <v>2.55</v>
+        <v>3.18</v>
       </c>
       <c r="Q31">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="R31">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -6795,10 +6795,10 @@
         <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E32" t="s">
         <v>144</v>
@@ -6834,13 +6834,13 @@
         <v>222</v>
       </c>
       <c r="P32">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -6980,7 +6980,7 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D33" t="s">
         <v>113</v>
@@ -7019,13 +7019,13 @@
         <v>222</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -7165,10 +7165,10 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E34" t="s">
         <v>146</v>
@@ -7350,7 +7350,7 @@
         <v>75</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D35" t="s">
         <v>112</v>
@@ -7389,13 +7389,13 @@
         <v>222</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -7535,7 +7535,7 @@
         <v>75</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D36" t="s">
         <v>112</v>
@@ -7574,13 +7574,13 @@
         <v>222</v>
       </c>
       <c r="P36">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7720,7 +7720,7 @@
         <v>75</v>
       </c>
       <c r="C37" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D37" t="s">
         <v>112</v>
@@ -9755,7 +9755,7 @@
         <v>80</v>
       </c>
       <c r="C48" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D48" t="s">
         <v>112</v>
@@ -9943,7 +9943,7 @@
         <v>108</v>
       </c>
       <c r="D49" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E49" t="s">
         <v>161</v>
@@ -10310,7 +10310,7 @@
         <v>81</v>
       </c>
       <c r="C51" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D51" t="s">
         <v>112</v>
@@ -10495,7 +10495,7 @@
         <v>81</v>
       </c>
       <c r="C52" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D52" t="s">
         <v>112</v>
@@ -10531,7 +10531,7 @@
         <v>-1</v>
       </c>
       <c r="O52" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P52">
         <v>0</v>
@@ -10680,10 +10680,10 @@
         <v>81</v>
       </c>
       <c r="C53" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D53" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E53" t="s">
         <v>165</v>
@@ -10719,13 +10719,13 @@
         <v>222</v>
       </c>
       <c r="P53">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q53">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -10865,10 +10865,10 @@
         <v>81</v>
       </c>
       <c r="C54" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D54" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E54" t="s">
         <v>166</v>
@@ -10904,13 +10904,13 @@
         <v>222</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -11050,10 +11050,10 @@
         <v>81</v>
       </c>
       <c r="C55" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D55" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E55" t="s">
         <v>167</v>
@@ -11086,7 +11086,7 @@
         <v>-1</v>
       </c>
       <c r="O55" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P55">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -268,12 +268,12 @@
     <t>Russia Russian Premier League</t>
   </si>
   <si>
+    <t>Ethiopia Ethiopia Premier League</t>
+  </si>
+  <si>
     <t>Indonesia Liga 1</t>
   </si>
   <si>
-    <t>Ethiopia Ethiopia Premier League</t>
-  </si>
-  <si>
     <t>India Indian Super League</t>
   </si>
   <si>
@@ -286,15 +286,15 @@
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
+    <t>Latvia Virsliga</t>
+  </si>
+  <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
-    <t>Latvia Virsliga</t>
-  </si>
-  <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
@@ -307,21 +307,21 @@
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
@@ -331,24 +331,24 @@
     <t>Italy Serie A</t>
   </si>
   <si>
+    <t>Bolivia LFPB</t>
+  </si>
+  <si>
     <t>Spain La Liga</t>
   </si>
   <si>
     <t>England Premier League</t>
   </si>
   <si>
-    <t>Bolivia LFPB</t>
+    <t>Israel Israeli Premier League</t>
+  </si>
+  <si>
+    <t>Algeria Ligue 1</t>
   </si>
   <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Israel Israeli Premier League</t>
-  </si>
-  <si>
-    <t>Algeria Ligue 1</t>
-  </si>
-  <si>
     <t>Ecuador Primera Categoría Serie A</t>
   </si>
   <si>
@@ -367,15 +367,15 @@
     <t>Ural</t>
   </si>
   <si>
+    <t>Ethiopian Medhin</t>
+  </si>
+  <si>
+    <t>Bali United</t>
+  </si>
+  <si>
     <t>Bhayangkara</t>
   </si>
   <si>
-    <t>Bali United</t>
-  </si>
-  <si>
-    <t>Ethiopian Medhin</t>
-  </si>
-  <si>
     <t>Olimpiyets</t>
   </si>
   <si>
@@ -400,18 +400,18 @@
     <t>Spaeri</t>
   </si>
   <si>
+    <t>Grobiņa</t>
+  </si>
+  <si>
+    <t>Metaloglobus</t>
+  </si>
+  <si>
     <t>Opava</t>
   </si>
   <si>
-    <t>Grobiņa</t>
-  </si>
-  <si>
     <t>Dinamo Jug</t>
   </si>
   <si>
-    <t>Metaloglobus</t>
-  </si>
-  <si>
     <t>Malmö FF W</t>
   </si>
   <si>
@@ -433,30 +433,30 @@
     <t>Neom SC</t>
   </si>
   <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
     <t>Madrid CFF</t>
   </si>
   <si>
+    <t>Rustavi</t>
+  </si>
+  <si>
+    <t>Sirius</t>
+  </si>
+  <si>
     <t>Randers</t>
   </si>
   <si>
+    <t>Dinamo Moskva</t>
+  </si>
+  <si>
     <t>Cracovia Kraków</t>
   </si>
   <si>
-    <t>Super Nova</t>
-  </si>
-  <si>
-    <t>Dinamo Moskva</t>
-  </si>
-  <si>
-    <t>Sirius</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Rustavi</t>
-  </si>
-  <si>
     <t>FCSB</t>
   </si>
   <si>
@@ -466,10 +466,13 @@
     <t>Yacoub El Mansour</t>
   </si>
   <si>
+    <t>Yverdon Sport</t>
+  </si>
+  <si>
     <t>Vaduz</t>
   </si>
   <si>
-    <t>Yverdon Sport</t>
+    <t>Neuchâtel Xamax</t>
   </si>
   <si>
     <t>Bellinzona</t>
@@ -478,48 +481,45 @@
     <t>Stade Nyonnais</t>
   </si>
   <si>
-    <t>Neuchâtel Xamax</t>
-  </si>
-  <si>
     <t>SD Huesca</t>
   </si>
   <si>
     <t>Napoli</t>
   </si>
   <si>
+    <t>ABB</t>
+  </si>
+  <si>
     <t>Rayo Vallecano</t>
   </si>
   <si>
     <t>Tottenham Hotspur</t>
   </si>
   <si>
-    <t>ABB</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
     <t>Curicó Unido</t>
   </si>
   <si>
+    <t>Mushuc Runa SC</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>Mushuc Runa SC</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
     <t>Arsenal Tula</t>
   </si>
   <si>
@@ -529,15 +529,15 @@
     <t>KAMAZ</t>
   </si>
   <si>
+    <t>Ethiopia Nigd Bank</t>
+  </si>
+  <si>
+    <t>Borneo</t>
+  </si>
+  <si>
     <t>Madura United</t>
   </si>
   <si>
-    <t>Borneo</t>
-  </si>
-  <si>
-    <t>Ethiopia Nigd Bank</t>
-  </si>
-  <si>
     <t>CSKA Moskva</t>
   </si>
   <si>
@@ -562,18 +562,18 @@
     <t>Gagra</t>
   </si>
   <si>
+    <t>FS Jelgava</t>
+  </si>
+  <si>
+    <t>Hermannstadt</t>
+  </si>
+  <si>
     <t>Líšeň</t>
   </si>
   <si>
-    <t>FS Jelgava</t>
-  </si>
-  <si>
     <t>Tekstilac Odžaci</t>
   </si>
   <si>
-    <t>Hermannstadt</t>
-  </si>
-  <si>
     <t>Häcken W</t>
   </si>
   <si>
@@ -595,30 +595,30 @@
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>Tukums</t>
+  </si>
+  <si>
+    <t>Odd</t>
+  </si>
+  <si>
     <t>Sevilla W</t>
   </si>
   <si>
+    <t>Dinamo Tbilisi</t>
+  </si>
+  <si>
+    <t>Örgryte</t>
+  </si>
+  <si>
     <t>OB</t>
   </si>
   <si>
+    <t>Krasnodar</t>
+  </si>
+  <si>
     <t>Radomiak Radom</t>
   </si>
   <si>
-    <t>Tukums</t>
-  </si>
-  <si>
-    <t>Krasnodar</t>
-  </si>
-  <si>
-    <t>Örgryte</t>
-  </si>
-  <si>
-    <t>Odd</t>
-  </si>
-  <si>
-    <t>Dinamo Tbilisi</t>
-  </si>
-  <si>
     <t>Unirea Slobozia</t>
   </si>
   <si>
@@ -628,10 +628,13 @@
     <t>Kawkab Marrakech</t>
   </si>
   <si>
+    <t>Rapperswil-Jona</t>
+  </si>
+  <si>
     <t>Aarau</t>
   </si>
   <si>
-    <t>Rapperswil-Jona</t>
+    <t>Étoile Carouge</t>
   </si>
   <si>
     <t>Wil</t>
@@ -640,46 +643,43 @@
     <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
-    <t>Étoile Carouge</t>
-  </si>
-  <si>
     <t>Real Sociedad II</t>
   </si>
   <si>
     <t>Bologna</t>
   </si>
   <si>
+    <t>Oriente Petrolero</t>
+  </si>
+  <si>
     <t>Girona FC</t>
   </si>
   <si>
     <t>Leeds United</t>
   </si>
   <si>
-    <t>Oriente Petrolero</t>
-  </si>
-  <si>
     <t>Olympique Dcheïra</t>
   </si>
   <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
     <t>San Marcos</t>
   </si>
   <si>
+    <t>LDU Quito</t>
+  </si>
+  <si>
+    <t>Hapoel Petah Tikva</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
     <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Hapoel Petah Tikva</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>LDU Quito</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1985,7 +1985,7 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
         <v>112</v>
@@ -2540,7 +2540,7 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
         <v>112</v>
@@ -3838,7 +3838,7 @@
         <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E16" t="s">
         <v>128</v>
@@ -4023,7 +4023,7 @@
         <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E17" t="s">
         <v>129</v>
@@ -4059,13 +4059,13 @@
         <v>222</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
         <v>112</v>
@@ -4390,7 +4390,7 @@
         <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
         <v>112</v>
@@ -4429,13 +4429,13 @@
         <v>222</v>
       </c>
       <c r="P19">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E27" t="s">
         <v>139</v>
@@ -6055,10 +6055,10 @@
         <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D28" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E28" t="s">
         <v>140</v>
@@ -6094,13 +6094,13 @@
         <v>222</v>
       </c>
       <c r="P28">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="Q28">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R28">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -6240,7 +6240,7 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D29" t="s">
         <v>112</v>
@@ -6425,7 +6425,7 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
         <v>113</v>
@@ -6610,10 +6610,10 @@
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s">
         <v>143</v>
@@ -6649,13 +6649,13 @@
         <v>222</v>
       </c>
       <c r="P31">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -6798,7 +6798,7 @@
         <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E32" t="s">
         <v>144</v>
@@ -6834,13 +6834,13 @@
         <v>222</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -6980,10 +6980,10 @@
         <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D33" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E33" t="s">
         <v>145</v>
@@ -7019,13 +7019,13 @@
         <v>222</v>
       </c>
       <c r="P33">
-        <v>2.55</v>
+        <v>3.18</v>
       </c>
       <c r="Q33">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="R33">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -7165,10 +7165,10 @@
         <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="D34" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E34" t="s">
         <v>146</v>
@@ -7350,7 +7350,7 @@
         <v>75</v>
       </c>
       <c r="C35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D35" t="s">
         <v>112</v>
@@ -9203,7 +9203,7 @@
         <v>105</v>
       </c>
       <c r="D45" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E45" t="s">
         <v>157</v>
@@ -9424,13 +9424,13 @@
         <v>222</v>
       </c>
       <c r="P46">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q46">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R46">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -9573,7 +9573,7 @@
         <v>107</v>
       </c>
       <c r="D47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E47" t="s">
         <v>159</v>
@@ -9609,13 +9609,13 @@
         <v>222</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -9943,7 +9943,7 @@
         <v>108</v>
       </c>
       <c r="D49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E49" t="s">
         <v>161</v>
@@ -10161,7 +10161,7 @@
         <v>-1</v>
       </c>
       <c r="O50" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P50">
         <v>0</v>
@@ -10310,10 +10310,10 @@
         <v>81</v>
       </c>
       <c r="C51" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D51" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E51" t="s">
         <v>163</v>
@@ -10495,10 +10495,10 @@
         <v>81</v>
       </c>
       <c r="C52" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D52" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E52" t="s">
         <v>164</v>
@@ -10534,13 +10534,13 @@
         <v>222</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -10680,7 +10680,7 @@
         <v>81</v>
       </c>
       <c r="C53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D53" t="s">
         <v>112</v>
@@ -10865,10 +10865,10 @@
         <v>81</v>
       </c>
       <c r="C54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D54" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E54" t="s">
         <v>166</v>
@@ -10904,13 +10904,13 @@
         <v>222</v>
       </c>
       <c r="P54">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q54">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R54">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -11050,7 +11050,7 @@
         <v>81</v>
       </c>
       <c r="C55" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D55" t="s">
         <v>112</v>
@@ -11086,7 +11086,7 @@
         <v>-1</v>
       </c>
       <c r="O55" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P55">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.28</v>
+        <v>3.18</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.85</v>
+        <v>3.67</v>
       </c>
       <c r="R32" t="n">
-        <v>8.65</v>
+        <v>2.33</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.55</v>
+        <v>1.28</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>5.85</v>
       </c>
       <c r="R33" t="n">
-        <v>2.5</v>
+        <v>8.65</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G56" t="n">

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.18</v>
+        <v>2.27</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>2.33</v>
+        <v>2.87</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.55</v>
+        <v>1.28</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>5.85</v>
       </c>
       <c r="R29" t="n">
-        <v>2.5</v>
+        <v>8.65</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6171,10 +6171,10 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6171,10 +6171,10 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G56" t="n">

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI56"/>
+  <dimension ref="A1:BI55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46153.54166666666</v>
+        <v>46153.5</v>
       </c>
     </row>
     <row r="21">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46153.5625</v>
+        <v>46153.54166666666</v>
       </c>
     </row>
     <row r="23">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46153.57291666666</v>
+        <v>46153.5625</v>
       </c>
     </row>
     <row r="25">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46153.57638888889</v>
+        <v>46153.57291666666</v>
       </c>
     </row>
     <row r="27">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46153.58333333334</v>
+        <v>46153.57638888889</v>
       </c>
     </row>
     <row r="28">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.18</v>
+        <v>1.28</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.67</v>
+        <v>5.85</v>
       </c>
       <c r="R29" t="n">
-        <v>2.33</v>
+        <v>8.65</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6171,10 +6171,10 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7249,27 +7249,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46153.625</v>
+        <v>46153.58333333334</v>
       </c>
     </row>
     <row r="36">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7840,12 +7840,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46153.63541666666</v>
+        <v>46153.625</v>
       </c>
     </row>
     <row r="39">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
-        <v>46153.64583333334</v>
+        <v>46153.63541666666</v>
       </c>
     </row>
     <row r="44">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.61</v>
+        <v>2.04</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.3</v>
+        <v>3.47</v>
       </c>
       <c r="R44" t="n">
-        <v>6.24</v>
+        <v>3.78</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
-        <v>46153.65625</v>
+        <v>46153.64583333334</v>
       </c>
     </row>
     <row r="45">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46153.66666666666</v>
+        <v>46153.65625</v>
       </c>
     </row>
     <row r="46">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10007,12 +10007,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46153.70833333334</v>
+        <v>46153.66666666666</v>
       </c>
     </row>
     <row r="50">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46153.875</v>
+        <v>46153.70833333334</v>
       </c>
     </row>
     <row r="51">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11377,203 +11377,6 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46153.875</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>USM Alger</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>ES Mostaganem</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N56" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI56" s="3" t="n">
         <v>46153.875</v>
       </c>
     </row>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6171,10 +6171,10 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.55</v>
+        <v>3.18</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="R33" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.28</v>
+        <v>3.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.85</v>
+        <v>3.67</v>
       </c>
       <c r="R30" t="n">
-        <v>8.65</v>
+        <v>2.33</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.18</v>
+        <v>1.28</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.67</v>
+        <v>5.85</v>
       </c>
       <c r="R33" t="n">
-        <v>2.33</v>
+        <v>8.65</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3.18</v>
+        <v>2.55</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.27</v>
+        <v>3.18</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="R31" t="n">
-        <v>2.87</v>
+        <v>2.33</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.28</v>
+        <v>2.27</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.85</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>8.65</v>
+        <v>2.87</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7353,10 +7353,10 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.61</v>
+        <v>3.39</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.39</v>
+        <v>3.61</v>
       </c>
       <c r="R3" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>5.85</v>
       </c>
       <c r="R33" t="n">
-        <v>2.87</v>
+        <v>8.65</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.28</v>
+        <v>2.27</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.85</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>8.65</v>
+        <v>2.87</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7353,10 +7353,10 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.39</v>
+        <v>3.61</v>
       </c>
       <c r="R2" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.61</v>
+        <v>3.39</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.18</v>
+        <v>1.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.67</v>
+        <v>3.52</v>
       </c>
       <c r="R28" t="n">
-        <v>2.33</v>
+        <v>3.73</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.61</v>
+        <v>3.39</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.39</v>
+        <v>3.61</v>
       </c>
       <c r="R3" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>3.73</v>
+        <v>2.5</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.28</v>
+        <v>2.27</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.85</v>
+        <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>8.65</v>
+        <v>2.87</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI55"/>
+  <dimension ref="A1:BI54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.55</v>
+        <v>1.28</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>5.85</v>
       </c>
       <c r="R28" t="n">
-        <v>2.5</v>
+        <v>8.65</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5974,10 +5974,10 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.18</v>
+        <v>2.27</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>2.33</v>
+        <v>2.87</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.28</v>
+        <v>2.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.85</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>8.65</v>
+        <v>2.5</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.92</v>
+        <v>3.18</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.52</v>
+        <v>3.67</v>
       </c>
       <c r="R33" t="n">
-        <v>3.73</v>
+        <v>2.33</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11180,203 +11180,6 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46153.875</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>USM Alger</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>ES Mostaganem</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI55" s="3" t="n">
         <v>46153.875</v>
       </c>
     </row>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.39</v>
+        <v>3.61</v>
       </c>
       <c r="R2" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.61</v>
+        <v>3.39</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5974,10 +5974,10 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.27</v>
+        <v>1.92</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R29" t="n">
-        <v>2.87</v>
+        <v>3.73</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.92</v>
+        <v>1.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.52</v>
+        <v>5.85</v>
       </c>
       <c r="R30" t="n">
-        <v>3.73</v>
+        <v>8.65</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,16 +6362,16 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI54"/>
+  <dimension ref="A1:BI63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.27</v>
+        <v>3.18</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="R34" t="n">
-        <v>2.87</v>
+        <v>2.33</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46153.70833333334</v>
+        <v>46153.67708333334</v>
       </c>
     </row>
     <row r="51">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR51" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY51" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA51" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB51" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF51" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46153.875</v>
+        <v>46153.67708333334</v>
       </c>
     </row>
     <row r="52">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR52" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS52" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW52" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX52" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY52" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BA52" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BB52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD52" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF52" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46153.875</v>
+        <v>46153.67708333334</v>
       </c>
     </row>
     <row r="53">
@@ -10795,27 +10795,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR53" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS53" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU53" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV53" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW53" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX53" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ53" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BB53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD53" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF53" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46153.875</v>
+        <v>46153.67708333334</v>
       </c>
     </row>
     <row r="54">
@@ -10992,27 +10992,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,141 +11045,1914 @@
         </is>
       </c>
       <c r="P54" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R54" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U54" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W54" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X54" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI54" s="3" t="n">
+        <v>46153.67708333334</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Rio Ave FC</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI55" s="3" t="n">
+        <v>46153.67708333334</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Vitória Guimarães</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Casa Pia</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="R56" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W56" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI56" s="3" t="n">
+        <v>46153.67708333334</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Morocco Botola Pro</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>CR Khemis Zemamra</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Olympique Dcheïra</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI57" s="3" t="n">
+        <v>46153.70833333334</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Ferro Carril Oeste</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Defensores de Belgrano</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R58" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U58" t="n">
+        <v>5</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W58" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="X58" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI58" s="3" t="n">
+        <v>46153.79166666666</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Nueva Chicago</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q59" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="R59" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S59" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U59" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W59" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="X59" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI59" s="3" t="n">
+        <v>46153.8125</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Curicó Unido</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI60" s="3" t="n">
+        <v>46153.875</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>USM Alger</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ES Mostaganem</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI61" s="3" t="n">
+        <v>46153.875</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Mushuc Runa SC</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q62" t="n">
         <v>3.2</v>
       </c>
-      <c r="R54" t="n">
+      <c r="R62" t="n">
         <v>2.3</v>
       </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI54" s="3" t="n">
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI62" s="3" t="n">
+        <v>46153.875</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>JS Saoura</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>CR Belouizdad</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N63" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI63" s="3" t="n">
         <v>46153.875</v>
       </c>
     </row>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.55</v>
+        <v>1.28</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>5.85</v>
       </c>
       <c r="R32" t="n">
-        <v>2.5</v>
+        <v>8.65</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3.18</v>
+        <v>1.92</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.67</v>
+        <v>3.52</v>
       </c>
       <c r="R34" t="n">
-        <v>2.33</v>
+        <v>3.73</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.36</v>
+        <v>2.08</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.98</v>
+        <v>3.34</v>
       </c>
       <c r="R50" t="n">
-        <v>8.199999999999999</v>
+        <v>3.66</v>
       </c>
       <c r="S50" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="T50" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="U50" t="n">
-        <v>7.1</v>
+        <v>4</v>
       </c>
       <c r="V50" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="W50" t="n">
-        <v>3.3</v>
+        <v>2.59</v>
       </c>
       <c r="X50" t="n">
-        <v>2.39</v>
+        <v>2.94</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="Z50" t="n">
-        <v>5.55</v>
+        <v>7</v>
       </c>
       <c r="AA50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ50" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1.18</v>
       </c>
       <c r="AK50" t="n">
         <v>1.8</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AN50" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.45</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AS50" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AT50" t="n">
         <v>2.75</v>
       </c>
       <c r="AU50" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AV50" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AY50" t="n">
         <v>1.37</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="BA50" t="n">
-        <v>4.75</v>
+        <v>2.8</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="BD50" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.34</v>
+        <v>3.46</v>
       </c>
       <c r="R51" t="n">
-        <v>3.66</v>
+        <v>3.76</v>
       </c>
       <c r="S51" t="n">
         <v>2.5</v>
@@ -10469,25 +10469,25 @@
         <v>2.15</v>
       </c>
       <c r="U51" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="V51" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W51" t="n">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="X51" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z51" t="n">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB51" t="n">
         <v>1.06</v>
@@ -10517,55 +10517,55 @@
         <v>1.08</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AM51" t="n">
         <v>1.3</v>
       </c>
       <c r="AN51" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="AU51" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AV51" t="n">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="BA51" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="BB51" t="n">
         <v>1.29</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="R52" t="n">
-        <v>1.98</v>
+        <v>4.82</v>
       </c>
       <c r="S52" t="n">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
       <c r="T52" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U52" t="n">
-        <v>2.54</v>
+        <v>4.8</v>
       </c>
       <c r="V52" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W52" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="X52" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z52" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AA52" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB52" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB52" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC52" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AE52" t="n">
         <v>1.8</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG52" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI52" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AJ52" t="n">
         <v>1.13</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL52" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN52" t="n">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AT52" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AZ52" t="n">
-        <v>2.8</v>
+        <v>1.38</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.56</v>
+        <v>3.5</v>
       </c>
       <c r="BB52" t="n">
         <v>1.22</v>
       </c>
       <c r="BC52" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE52" t="n">
         <v>1.73</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.71</v>
+        <v>11.5</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.82</v>
+        <v>6.6</v>
       </c>
       <c r="R53" t="n">
-        <v>4.82</v>
+        <v>1.2</v>
       </c>
       <c r="S53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AF53" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AI53" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU53" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV53" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW53" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BA53" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.46</v>
+        <v>3.84</v>
       </c>
       <c r="R54" t="n">
-        <v>3.76</v>
+        <v>4.36</v>
       </c>
       <c r="S54" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="T54" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U54" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="V54" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="W54" t="n">
-        <v>2.69</v>
+        <v>2.99</v>
       </c>
       <c r="X54" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z54" t="n">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AF54" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK54" t="n">
         <v>1.75</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AL54" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD54" t="n">
         <v>3.6</v>
       </c>
-      <c r="AH54" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC54" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD54" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BE54" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>11.5</v>
+        <v>1.36</v>
       </c>
       <c r="Q55" t="n">
-        <v>6.6</v>
+        <v>4.98</v>
       </c>
       <c r="R55" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U55" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X55" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB55" t="n">
         <v>1.2</v>
       </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>0</v>
-      </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,28 +11439,28 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.77</v>
+        <v>3.72</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.84</v>
+        <v>3.58</v>
       </c>
       <c r="R56" t="n">
-        <v>4.36</v>
+        <v>1.98</v>
       </c>
       <c r="S56" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="T56" t="n">
         <v>2.25</v>
       </c>
       <c r="U56" t="n">
-        <v>4.33</v>
+        <v>2.54</v>
       </c>
       <c r="V56" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W56" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="X56" t="n">
         <v>2.73</v>
@@ -11469,7 +11469,7 @@
         <v>1.4</v>
       </c>
       <c r="Z56" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="AA56" t="n">
         <v>1.04</v>
@@ -11481,91 +11481,91 @@
         <v>1.25</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU56" t="n">
         <v>3.2</v>
       </c>
-      <c r="AH56" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AV56" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AW56" t="n">
-        <v>2.07</v>
+        <v>1.84</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.35</v>
+        <v>2.8</v>
       </c>
       <c r="BA56" t="n">
-        <v>3.65</v>
+        <v>1.56</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC56" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BD56" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7353,10 +7353,10 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.08</v>
+        <v>11.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.34</v>
+        <v>6.6</v>
       </c>
       <c r="R50" t="n">
-        <v>3.66</v>
+        <v>1.2</v>
       </c>
       <c r="S50" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF50" t="n">
         <v>3.1</v>
       </c>
-      <c r="AE50" t="n">
+      <c r="AG50" t="n">
         <v>2.05</v>
       </c>
-      <c r="AF50" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AH50" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AI50" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV50" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BA50" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC50" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.71</v>
+        <v>3.72</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="R52" t="n">
-        <v>4.82</v>
+        <v>1.98</v>
       </c>
       <c r="S52" t="n">
-        <v>2.15</v>
+        <v>3.9</v>
       </c>
       <c r="T52" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U52" t="n">
-        <v>4.8</v>
+        <v>2.54</v>
       </c>
       <c r="V52" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W52" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="X52" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z52" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AE52" t="n">
         <v>1.8</v>
       </c>
       <c r="AF52" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI52" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AJ52" t="n">
         <v>1.13</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN52" t="n">
-        <v>2.15</v>
+        <v>1.29</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="AW52" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.38</v>
+        <v>2.8</v>
       </c>
       <c r="BA52" t="n">
-        <v>3.5</v>
+        <v>1.56</v>
       </c>
       <c r="BB52" t="n">
         <v>1.22</v>
       </c>
       <c r="BC52" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BE52" t="n">
         <v>1.73</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>11.5</v>
+        <v>1.71</v>
       </c>
       <c r="Q53" t="n">
-        <v>6.6</v>
+        <v>3.82</v>
       </c>
       <c r="R53" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W53" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X53" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF53" t="n">
         <v>1.2</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF53" t="n">
-        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.84</v>
+        <v>3.34</v>
       </c>
       <c r="R54" t="n">
-        <v>4.36</v>
+        <v>3.66</v>
       </c>
       <c r="S54" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="T54" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U54" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="V54" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="W54" t="n">
-        <v>2.99</v>
+        <v>2.59</v>
       </c>
       <c r="X54" t="n">
-        <v>2.73</v>
+        <v>2.94</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z54" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AA54" t="n">
         <v>1.04</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH54" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD54" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH54" t="n">
+      <c r="AI54" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM54" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI54" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK54" t="n">
+      <c r="AN54" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL54" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM54" t="n">
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB54" t="n">
         <v>1.29</v>
       </c>
-      <c r="AN54" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC54" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BD54" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.98</v>
+        <v>3.84</v>
       </c>
       <c r="R55" t="n">
-        <v>8.199999999999999</v>
+        <v>4.36</v>
       </c>
       <c r="S55" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="T55" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U55" t="n">
-        <v>7.1</v>
+        <v>4.33</v>
       </c>
       <c r="V55" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="W55" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="X55" t="n">
-        <v>2.39</v>
+        <v>2.73</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="Z55" t="n">
-        <v>5.55</v>
+        <v>6.9</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AD55" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AI55" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL55" t="n">
         <v>1.95</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AN55" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="AT55" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AU55" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="BA55" t="n">
-        <v>4.75</v>
+        <v>3.65</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC55" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.72</v>
+        <v>1.36</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.58</v>
+        <v>4.98</v>
       </c>
       <c r="R56" t="n">
-        <v>1.98</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S56" t="n">
-        <v>3.9</v>
+        <v>1.81</v>
       </c>
       <c r="T56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U56" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W56" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF56" t="n">
         <v>2.25</v>
       </c>
-      <c r="U56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="X56" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE56" t="n">
+      <c r="AG56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK56" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF56" t="n">
+      <c r="AL56" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AM56" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN56" t="n">
         <v>3</v>
       </c>
-      <c r="AH56" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AO56" t="n">
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AT56" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AU56" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AV56" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AZ56" t="n">
-        <v>2.8</v>
+        <v>1.23</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.56</v>
+        <v>4.75</v>
       </c>
       <c r="BB56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BF56" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.61</v>
+        <v>3.39</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.39</v>
+        <v>3.61</v>
       </c>
       <c r="R3" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>3.32</v>
+        <v>2.93</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R24" t="n">
-        <v>2.93</v>
+        <v>3.32</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.18</v>
+        <v>2.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7353,10 +7353,10 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>11.5</v>
+        <v>2.08</v>
       </c>
       <c r="Q50" t="n">
-        <v>6.6</v>
+        <v>3.34</v>
       </c>
       <c r="R50" t="n">
-        <v>1.2</v>
+        <v>3.66</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AF50" t="n">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.72</v>
+        <v>11.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.58</v>
+        <v>6.6</v>
       </c>
       <c r="R52" t="n">
-        <v>1.98</v>
+        <v>1.2</v>
       </c>
       <c r="S52" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
         <v>1.36</v>
       </c>
-      <c r="W52" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="X52" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF52" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="AG52" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AI52" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ52" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC52" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.71</v>
+        <v>3.72</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="R53" t="n">
-        <v>4.82</v>
+        <v>1.98</v>
       </c>
       <c r="S53" t="n">
-        <v>2.15</v>
+        <v>3.9</v>
       </c>
       <c r="T53" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U53" t="n">
-        <v>4.8</v>
+        <v>2.54</v>
       </c>
       <c r="V53" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W53" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="X53" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z53" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AE53" t="n">
         <v>1.8</v>
       </c>
       <c r="AF53" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI53" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AJ53" t="n">
         <v>1.13</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN53" t="n">
-        <v>2.15</v>
+        <v>1.29</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AU53" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="AV53" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="AW53" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.38</v>
+        <v>2.8</v>
       </c>
       <c r="BA53" t="n">
-        <v>3.5</v>
+        <v>1.56</v>
       </c>
       <c r="BB53" t="n">
         <v>1.22</v>
       </c>
       <c r="BC53" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BD53" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BE53" t="n">
         <v>1.73</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.34</v>
+        <v>3.84</v>
       </c>
       <c r="R54" t="n">
-        <v>3.66</v>
+        <v>4.36</v>
       </c>
       <c r="S54" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="T54" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U54" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="V54" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="W54" t="n">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
       <c r="X54" t="n">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z54" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AA54" t="n">
         <v>1.04</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AF54" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK54" t="n">
         <v>1.75</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AL54" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD54" t="n">
         <v>3.6</v>
       </c>
-      <c r="AH54" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC54" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD54" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BE54" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,67 +11242,67 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="R55" t="n">
-        <v>4.36</v>
+        <v>4.82</v>
       </c>
       <c r="S55" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T55" t="n">
         <v>2.3</v>
       </c>
-      <c r="T55" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U55" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="V55" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W55" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="X55" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z55" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="AA55" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB55" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB55" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC55" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG55" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI55" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK55" t="n">
         <v>1.75</v>
@@ -11311,64 +11311,64 @@
         <v>1.95</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AN55" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AQ55" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ55" t="n">
         <v>1.38</v>
       </c>
-      <c r="AR55" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>1.35</v>
-      </c>
       <c r="BA55" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC55" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G63" t="n">

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.39</v>
+        <v>3.61</v>
       </c>
       <c r="R2" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.61</v>
+        <v>3.39</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.65</v>
+        <v>2.48</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.92</v>
+        <v>1.28</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.52</v>
+        <v>5.85</v>
       </c>
       <c r="R33" t="n">
-        <v>3.73</v>
+        <v>8.65</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,16 +6953,16 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.34</v>
+        <v>4.98</v>
       </c>
       <c r="R50" t="n">
-        <v>3.66</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S50" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T50" t="n">
         <v>2.5</v>
       </c>
-      <c r="T50" t="n">
-        <v>2.15</v>
-      </c>
       <c r="U50" t="n">
-        <v>4</v>
+        <v>7.1</v>
       </c>
       <c r="V50" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W50" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X50" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH50" t="n">
         <v>1.44</v>
       </c>
-      <c r="W50" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI50" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AK50" t="n">
         <v>1.8</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AN50" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.45</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AS50" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AT50" t="n">
         <v>2.75</v>
       </c>
       <c r="AU50" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AV50" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AY50" t="n">
         <v>1.37</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="BA50" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BC50" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="BD50" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.46</v>
+        <v>3.84</v>
       </c>
       <c r="R51" t="n">
-        <v>3.76</v>
+        <v>4.36</v>
       </c>
       <c r="S51" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="T51" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U51" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="V51" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="W51" t="n">
-        <v>2.69</v>
+        <v>2.99</v>
       </c>
       <c r="X51" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z51" t="n">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AE51" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AF51" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK51" t="n">
         <v>1.75</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AL51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD51" t="n">
         <v>3.6</v>
       </c>
-      <c r="AH51" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BE51" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>11.5</v>
+        <v>2.08</v>
       </c>
       <c r="Q52" t="n">
-        <v>6.6</v>
+        <v>3.34</v>
       </c>
       <c r="R52" t="n">
-        <v>1.2</v>
+        <v>3.66</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AF52" t="n">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR52" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU52" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW52" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX52" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY52" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA52" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB52" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD52" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF52" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="R53" t="n">
-        <v>1.98</v>
+        <v>4.82</v>
       </c>
       <c r="S53" t="n">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
       <c r="T53" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U53" t="n">
-        <v>2.54</v>
+        <v>4.8</v>
       </c>
       <c r="V53" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W53" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="X53" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z53" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AA53" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB53" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB53" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC53" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AE53" t="n">
         <v>1.8</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG53" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI53" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AJ53" t="n">
         <v>1.13</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL53" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN53" t="n">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AT53" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AU53" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AV53" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AZ53" t="n">
-        <v>2.8</v>
+        <v>1.38</v>
       </c>
       <c r="BA53" t="n">
-        <v>1.56</v>
+        <v>3.5</v>
       </c>
       <c r="BB53" t="n">
         <v>1.22</v>
       </c>
       <c r="BC53" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BD53" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE53" t="n">
         <v>1.73</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.77</v>
+        <v>11.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.84</v>
+        <v>6.6</v>
       </c>
       <c r="R54" t="n">
-        <v>4.36</v>
+        <v>1.2</v>
       </c>
       <c r="S54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="AG54" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AI54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU54" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV54" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AW54" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BA54" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC54" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD54" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.82</v>
+        <v>3.46</v>
       </c>
       <c r="R55" t="n">
-        <v>4.82</v>
+        <v>3.76</v>
       </c>
       <c r="S55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T55" t="n">
         <v>2.15</v>
       </c>
-      <c r="T55" t="n">
-        <v>2.3</v>
-      </c>
       <c r="U55" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="V55" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W55" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X55" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX55" t="n">
         <v>1.35</v>
       </c>
-      <c r="W55" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X55" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AY55" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="BA55" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BC55" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V56" t="n">
         <v>1.36</v>
       </c>
-      <c r="Q56" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="R56" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="S56" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="T56" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U56" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="V56" t="n">
+      <c r="W56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
         <v>1.28</v>
       </c>
-      <c r="W56" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X56" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC56" t="n">
+      <c r="AQ56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF56" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G63" t="n">

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.61</v>
+        <v>3.39</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.39</v>
+        <v>3.61</v>
       </c>
       <c r="R3" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.78</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="R10" t="n">
-        <v>2.77</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>2.93</v>
+        <v>3.32</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>3.32</v>
+        <v>2.93</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="R31" t="n">
-        <v>2.5</v>
+        <v>3.73</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.18</v>
+        <v>2.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.27</v>
+        <v>3.18</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="R34" t="n">
-        <v>2.87</v>
+        <v>2.33</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="R35" t="n">
-        <v>3.73</v>
+        <v>2.84</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.98</v>
+        <v>3.84</v>
       </c>
       <c r="R50" t="n">
-        <v>8.199999999999999</v>
+        <v>4.36</v>
       </c>
       <c r="S50" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="T50" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U50" t="n">
-        <v>7.1</v>
+        <v>4.33</v>
       </c>
       <c r="V50" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="W50" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="X50" t="n">
-        <v>2.39</v>
+        <v>2.73</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="Z50" t="n">
-        <v>5.55</v>
+        <v>6.9</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AD50" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AI50" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL50" t="n">
         <v>1.95</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AN50" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AS50" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AU50" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="AV50" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="BA50" t="n">
-        <v>4.75</v>
+        <v>3.65</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="BD50" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.84</v>
+        <v>3.46</v>
       </c>
       <c r="R51" t="n">
-        <v>4.36</v>
+        <v>3.76</v>
       </c>
       <c r="S51" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="T51" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W51" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X51" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC51" t="n">
         <v>2.25</v>
       </c>
-      <c r="U51" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W51" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="X51" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>2.1</v>
-      </c>
       <c r="BD51" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.34</v>
+        <v>4.98</v>
       </c>
       <c r="R52" t="n">
-        <v>3.66</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S52" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T52" t="n">
         <v>2.5</v>
       </c>
-      <c r="T52" t="n">
-        <v>2.15</v>
-      </c>
       <c r="U52" t="n">
-        <v>4</v>
+        <v>7.1</v>
       </c>
       <c r="V52" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W52" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH52" t="n">
         <v>1.44</v>
       </c>
-      <c r="W52" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X52" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI52" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AK52" t="n">
         <v>1.8</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AN52" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.45</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AT52" t="n">
         <v>2.75</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AY52" t="n">
         <v>1.37</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="BA52" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BC52" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.71</v>
+        <v>11.5</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.82</v>
+        <v>6.6</v>
       </c>
       <c r="R53" t="n">
-        <v>4.82</v>
+        <v>1.2</v>
       </c>
       <c r="S53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AF53" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AI53" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU53" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV53" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW53" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BA53" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>11.5</v>
+        <v>2.08</v>
       </c>
       <c r="Q54" t="n">
-        <v>6.6</v>
+        <v>3.34</v>
       </c>
       <c r="R54" t="n">
-        <v>1.2</v>
+        <v>3.66</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AF54" t="n">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX54" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA54" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB54" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF54" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R55" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W55" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X55" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF55" t="n">
         <v>2</v>
       </c>
-      <c r="Q55" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="R55" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T55" t="n">
+      <c r="AG55" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN55" t="n">
         <v>2.15</v>
       </c>
-      <c r="U55" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V55" t="n">
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ55" t="n">
         <v>1.41</v>
       </c>
-      <c r="W55" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X55" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN55" t="n">
+      <c r="AR55" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE55" t="n">
         <v>1.73</v>
       </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BF55" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G63" t="n">

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.39</v>
+        <v>3.61</v>
       </c>
       <c r="R2" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.61</v>
+        <v>3.39</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>3.32</v>
+        <v>2.93</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R24" t="n">
-        <v>2.93</v>
+        <v>3.32</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.27</v>
+        <v>3.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="R30" t="n">
-        <v>2.87</v>
+        <v>2.33</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.55</v>
+        <v>1.28</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>5.85</v>
       </c>
       <c r="R32" t="n">
-        <v>2.5</v>
+        <v>8.65</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.28</v>
+        <v>2.27</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.85</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>8.65</v>
+        <v>2.87</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.46</v>
+        <v>4.98</v>
       </c>
       <c r="R51" t="n">
-        <v>3.76</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S51" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T51" t="n">
         <v>2.5</v>
       </c>
-      <c r="T51" t="n">
-        <v>2.15</v>
-      </c>
       <c r="U51" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X51" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD51" t="n">
         <v>4.2</v>
       </c>
-      <c r="V51" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W51" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X51" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BE51" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
         <v>1.36</v>
       </c>
-      <c r="Q52" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="R52" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="S52" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U52" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W52" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AF52" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AI52" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BA52" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD52" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>11.5</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>6.6</v>
+        <v>3.46</v>
       </c>
       <c r="R53" t="n">
-        <v>1.2</v>
+        <v>3.76</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AF53" t="n">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR53" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS53" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AU53" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AV53" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AW53" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX53" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ53" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BA53" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BB53" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF53" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.08</v>
+        <v>3.72</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="R54" t="n">
-        <v>3.66</v>
+        <v>1.98</v>
       </c>
       <c r="S54" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="T54" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U54" t="n">
-        <v>4</v>
+        <v>2.54</v>
       </c>
       <c r="V54" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W54" t="n">
-        <v>2.59</v>
+        <v>2.89</v>
       </c>
       <c r="X54" t="n">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z54" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AA54" t="n">
         <v>1.04</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH54" t="n">
         <v>1.33</v>
       </c>
-      <c r="AD54" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE54" t="n">
+      <c r="AI54" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL54" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>1.91</v>
       </c>
       <c r="AM54" t="n">
         <v>1.3</v>
       </c>
       <c r="AN54" t="n">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AU54" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AV54" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="BA54" t="n">
-        <v>2.8</v>
+        <v>1.56</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BC54" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="BD54" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.82</v>
+        <v>3.34</v>
       </c>
       <c r="R55" t="n">
-        <v>4.82</v>
+        <v>3.66</v>
       </c>
       <c r="S55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T55" t="n">
         <v>2.15</v>
       </c>
-      <c r="T55" t="n">
-        <v>2.3</v>
-      </c>
       <c r="U55" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="V55" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W55" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X55" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y55" t="n">
         <v>1.35</v>
       </c>
-      <c r="W55" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X55" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.43</v>
-      </c>
       <c r="Z55" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AA55" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB55" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB55" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AC55" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="AE55" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK55" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK55" t="n">
+      <c r="AL55" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN55" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM55" t="n">
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN55" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AQ55" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AT55" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AU55" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AW55" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="BA55" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BC55" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="R56" t="n">
-        <v>1.98</v>
+        <v>4.82</v>
       </c>
       <c r="S56" t="n">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
       <c r="T56" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U56" t="n">
-        <v>2.54</v>
+        <v>4.8</v>
       </c>
       <c r="V56" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W56" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="X56" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z56" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AA56" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB56" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB56" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC56" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AE56" t="n">
         <v>1.8</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG56" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI56" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AJ56" t="n">
         <v>1.13</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL56" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AM56" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN56" t="n">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
       <c r="AO56" t="n">
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AT56" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AU56" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AV56" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AZ56" t="n">
-        <v>2.8</v>
+        <v>1.38</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.56</v>
+        <v>3.5</v>
       </c>
       <c r="BB56" t="n">
         <v>1.22</v>
       </c>
       <c r="BC56" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BD56" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE56" t="n">
         <v>1.73</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G63" t="n">

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.61</v>
+        <v>3.39</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.39</v>
+        <v>3.61</v>
       </c>
       <c r="R3" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>2.93</v>
+        <v>3.32</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>3.32</v>
+        <v>2.93</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3.18</v>
+        <v>1.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.67</v>
+        <v>5.85</v>
       </c>
       <c r="R30" t="n">
-        <v>2.33</v>
+        <v>8.65</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R35" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,28 +10257,28 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.77</v>
+        <v>3.72</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.84</v>
+        <v>3.58</v>
       </c>
       <c r="R50" t="n">
-        <v>4.36</v>
+        <v>1.98</v>
       </c>
       <c r="S50" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="T50" t="n">
         <v>2.25</v>
       </c>
       <c r="U50" t="n">
-        <v>4.33</v>
+        <v>2.54</v>
       </c>
       <c r="V50" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W50" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="X50" t="n">
         <v>2.73</v>
@@ -10287,7 +10287,7 @@
         <v>1.4</v>
       </c>
       <c r="Z50" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="AA50" t="n">
         <v>1.04</v>
@@ -10299,91 +10299,91 @@
         <v>1.25</v>
       </c>
       <c r="AD50" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU50" t="n">
         <v>3.2</v>
       </c>
-      <c r="AH50" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AV50" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AW50" t="n">
-        <v>2.07</v>
+        <v>1.84</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.35</v>
+        <v>2.8</v>
       </c>
       <c r="BA50" t="n">
-        <v>3.65</v>
+        <v>1.56</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC50" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BD50" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>11.5</v>
+        <v>1.77</v>
       </c>
       <c r="Q52" t="n">
-        <v>6.6</v>
+        <v>3.84</v>
       </c>
       <c r="R52" t="n">
-        <v>1.2</v>
+        <v>4.36</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AF52" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="AH52" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX52" t="n">
         <v>1.68</v>
       </c>
-      <c r="AI52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>0</v>
-      </c>
       <c r="AY52" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BA52" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BB52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD52" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF52" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3.72</v>
+        <v>11.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.58</v>
+        <v>6.6</v>
       </c>
       <c r="R54" t="n">
-        <v>1.98</v>
+        <v>1.2</v>
       </c>
       <c r="S54" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
         <v>1.36</v>
       </c>
-      <c r="W54" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF54" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="AG54" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AI54" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN54" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU54" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV54" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ54" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD54" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R55" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W55" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X55" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS55" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q55" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R55" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U55" t="n">
-        <v>4</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W55" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X55" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AT55" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AU55" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="BA55" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BC55" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.82</v>
+        <v>3.34</v>
       </c>
       <c r="R56" t="n">
-        <v>4.82</v>
+        <v>3.66</v>
       </c>
       <c r="S56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T56" t="n">
         <v>2.15</v>
       </c>
-      <c r="T56" t="n">
-        <v>2.3</v>
-      </c>
       <c r="U56" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="V56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W56" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y56" t="n">
         <v>1.35</v>
       </c>
-      <c r="W56" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X56" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.43</v>
-      </c>
       <c r="Z56" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AA56" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB56" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB56" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AC56" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="AE56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK56" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF56" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK56" t="n">
+      <c r="AL56" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN56" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM56" t="n">
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AQ56" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AT56" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AU56" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AV56" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AW56" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="BA56" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BC56" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BD56" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G63" t="n">

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI63"/>
+  <dimension ref="A1:BI61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.39</v>
+        <v>3.61</v>
       </c>
       <c r="R2" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.61</v>
+        <v>3.39</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="R11" t="n">
-        <v>2.77</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.28</v>
+        <v>2.55</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.85</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>8.65</v>
+        <v>2.5</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.92</v>
+        <v>3.18</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.52</v>
+        <v>3.67</v>
       </c>
       <c r="R31" t="n">
-        <v>3.73</v>
+        <v>2.33</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>5.85</v>
       </c>
       <c r="R33" t="n">
-        <v>2.87</v>
+        <v>8.65</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="R34" t="n">
-        <v>2.5</v>
+        <v>3.73</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.33</v>
+        <v>3.27</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="R39" t="n">
-        <v>2.65</v>
+        <v>1.99</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.6</v>
+        <v>2.33</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="R40" t="n">
-        <v>4.69</v>
+        <v>2.65</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.27</v>
+        <v>2.78</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="R42" t="n">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.98</v>
+        <v>3.46</v>
       </c>
       <c r="R51" t="n">
-        <v>8.199999999999999</v>
+        <v>3.76</v>
       </c>
       <c r="S51" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="T51" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="U51" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="V51" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="W51" t="n">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="X51" t="n">
-        <v>2.39</v>
+        <v>2.99</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="Z51" t="n">
-        <v>5.55</v>
+        <v>7.9</v>
       </c>
       <c r="AA51" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ51" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB51" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE51" t="n">
+      <c r="AK51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ51" t="n">
         <v>1.61</v>
       </c>
-      <c r="AF51" t="n">
+      <c r="BA51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC51" t="n">
         <v>2.25</v>
       </c>
-      <c r="AG51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BD51" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R53" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W53" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X53" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF53" t="n">
         <v>2</v>
       </c>
-      <c r="Q53" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="R53" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T53" t="n">
+      <c r="AG53" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN53" t="n">
         <v>2.15</v>
       </c>
-      <c r="U53" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V53" t="n">
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ53" t="n">
         <v>1.41</v>
       </c>
-      <c r="W53" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X53" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN53" t="n">
+      <c r="AR53" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE53" t="n">
         <v>1.73</v>
       </c>
-      <c r="AO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB53" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE53" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BF53" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>11.5</v>
+        <v>2.08</v>
       </c>
       <c r="Q54" t="n">
-        <v>6.6</v>
+        <v>3.34</v>
       </c>
       <c r="R54" t="n">
-        <v>1.2</v>
+        <v>3.66</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AF54" t="n">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX54" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA54" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB54" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF54" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.71</v>
+        <v>11.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.82</v>
+        <v>6.6</v>
       </c>
       <c r="R55" t="n">
-        <v>4.82</v>
+        <v>1.2</v>
       </c>
       <c r="S55" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AF55" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AI55" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN55" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT55" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU55" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BA55" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.34</v>
+        <v>4.98</v>
       </c>
       <c r="R56" t="n">
-        <v>3.66</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S56" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T56" t="n">
         <v>2.5</v>
       </c>
-      <c r="T56" t="n">
-        <v>2.15</v>
-      </c>
       <c r="U56" t="n">
-        <v>4</v>
+        <v>7.1</v>
       </c>
       <c r="V56" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W56" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH56" t="n">
         <v>1.44</v>
       </c>
-      <c r="W56" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X56" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI56" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AK56" t="n">
         <v>1.8</v>
       </c>
       <c r="AL56" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AM56" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AN56" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="AO56" t="n">
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.45</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AT56" t="n">
         <v>2.75</v>
       </c>
       <c r="AU56" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AV56" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AY56" t="n">
         <v>1.37</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="BA56" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BC56" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="BD56" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12559,400 +12559,6 @@
         <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>46153.875</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>JS Saoura</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>CR Belouizdad</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N62" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI62" s="3" t="n">
-        <v>46153.875</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Curicó Unido</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>San Marcos</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI63" s="3" t="n">
         <v>46153.875</v>
       </c>
     </row>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.61</v>
+        <v>3.39</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.39</v>
+        <v>3.61</v>
       </c>
       <c r="R3" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.78</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="R10" t="n">
-        <v>2.77</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.65</v>
+        <v>2.48</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="R30" t="n">
-        <v>2.5</v>
+        <v>3.73</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.18</v>
+        <v>1.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.67</v>
+        <v>5.85</v>
       </c>
       <c r="R31" t="n">
-        <v>2.33</v>
+        <v>8.65</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6565,10 +6565,10 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.31</v>
+        <v>3.18</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.25</v>
+        <v>3.67</v>
       </c>
       <c r="R32" t="n">
-        <v>2.84</v>
+        <v>2.33</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.28</v>
+        <v>2.27</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.85</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>8.65</v>
+        <v>2.87</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R35" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.78</v>
+        <v>1.6</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="R42" t="n">
-        <v>2.36</v>
+        <v>4.69</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.6</v>
+        <v>2.78</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="R43" t="n">
-        <v>4.69</v>
+        <v>2.36</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.72</v>
+        <v>2.08</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="R50" t="n">
-        <v>1.98</v>
+        <v>3.66</v>
       </c>
       <c r="S50" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="T50" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U50" t="n">
-        <v>2.54</v>
+        <v>4</v>
       </c>
       <c r="V50" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W50" t="n">
-        <v>2.89</v>
+        <v>2.59</v>
       </c>
       <c r="X50" t="n">
-        <v>2.73</v>
+        <v>2.94</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z50" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AA50" t="n">
         <v>1.04</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH50" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD50" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE50" t="n">
+      <c r="AI50" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK50" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF50" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AL50" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AM50" t="n">
         <v>1.3</v>
       </c>
       <c r="AN50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB50" t="n">
         <v>1.29</v>
       </c>
-      <c r="AO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC50" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="BD50" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.46</v>
+        <v>3.84</v>
       </c>
       <c r="R51" t="n">
-        <v>3.76</v>
+        <v>4.36</v>
       </c>
       <c r="S51" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="T51" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U51" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="V51" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="W51" t="n">
-        <v>2.69</v>
+        <v>2.99</v>
       </c>
       <c r="X51" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z51" t="n">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AE51" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AF51" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK51" t="n">
         <v>1.75</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AL51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD51" t="n">
         <v>3.6</v>
       </c>
-      <c r="AH51" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BE51" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.77</v>
+        <v>11.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.84</v>
+        <v>6.6</v>
       </c>
       <c r="R52" t="n">
-        <v>4.36</v>
+        <v>1.2</v>
       </c>
       <c r="S52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="AG52" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AI52" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AW52" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BA52" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC52" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.82</v>
+        <v>3.46</v>
       </c>
       <c r="R53" t="n">
-        <v>4.82</v>
+        <v>3.76</v>
       </c>
       <c r="S53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T53" t="n">
         <v>2.15</v>
       </c>
-      <c r="T53" t="n">
-        <v>2.3</v>
-      </c>
       <c r="U53" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="V53" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W53" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X53" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX53" t="n">
         <v>1.35</v>
       </c>
-      <c r="W53" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X53" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AY53" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="BA53" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BC53" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BD53" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R54" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W54" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X54" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS54" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q54" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R54" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U54" t="n">
-        <v>4</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W54" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AT54" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AU54" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AV54" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="BA54" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BC54" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BD54" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>11.5</v>
+        <v>3.72</v>
       </c>
       <c r="Q55" t="n">
-        <v>6.6</v>
+        <v>3.58</v>
       </c>
       <c r="R55" t="n">
-        <v>1.2</v>
+        <v>1.98</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AF55" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL55" t="n">
         <v>2.05</v>
       </c>
-      <c r="AH55" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>0</v>
-      </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BA55" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>3.64</v>
       </c>
       <c r="R18" t="n">
-        <v>2.48</v>
+        <v>1.65</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>3.32</v>
+        <v>2.93</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R24" t="n">
-        <v>2.93</v>
+        <v>3.32</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6565,10 +6565,10 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.18</v>
+        <v>1.28</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.67</v>
+        <v>5.85</v>
       </c>
       <c r="R32" t="n">
-        <v>2.33</v>
+        <v>8.65</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.27</v>
+        <v>3.18</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="R33" t="n">
-        <v>2.87</v>
+        <v>2.33</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3.27</v>
+        <v>1.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="R39" t="n">
-        <v>1.99</v>
+        <v>4.69</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.6</v>
+        <v>2.78</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="R42" t="n">
-        <v>4.69</v>
+        <v>2.36</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.78</v>
+        <v>3.27</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="R43" t="n">
-        <v>2.36</v>
+        <v>1.99</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R50" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W50" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X50" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS50" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q50" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R50" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U50" t="n">
-        <v>4</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W50" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AT50" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AU50" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AV50" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="BA50" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BC50" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BD50" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.84</v>
+        <v>4.98</v>
       </c>
       <c r="R51" t="n">
-        <v>4.36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S51" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="T51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U51" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X51" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF51" t="n">
         <v>2.25</v>
       </c>
-      <c r="U51" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W51" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="X51" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AG51" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI51" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL51" t="n">
         <v>1.95</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AN51" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AU51" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="AV51" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="AW51" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="BA51" t="n">
-        <v>3.65</v>
+        <v>4.75</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC51" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>11.5</v>
+        <v>1.77</v>
       </c>
       <c r="Q52" t="n">
-        <v>6.6</v>
+        <v>3.84</v>
       </c>
       <c r="R52" t="n">
-        <v>1.2</v>
+        <v>4.36</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AF52" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="AH52" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX52" t="n">
         <v>1.68</v>
       </c>
-      <c r="AI52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>0</v>
-      </c>
       <c r="AY52" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BA52" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BB52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD52" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF52" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.46</v>
+        <v>3.34</v>
       </c>
       <c r="R53" t="n">
-        <v>3.76</v>
+        <v>3.66</v>
       </c>
       <c r="S53" t="n">
         <v>2.5</v>
@@ -10863,25 +10863,25 @@
         <v>2.15</v>
       </c>
       <c r="U53" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="V53" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W53" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="X53" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z53" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB53" t="n">
         <v>1.06</v>
@@ -10911,55 +10911,55 @@
         <v>1.08</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AM53" t="n">
         <v>1.3</v>
       </c>
       <c r="AN53" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="AR53" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="AT53" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="AU53" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="AV53" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="BA53" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="BB53" t="n">
         <v>1.29</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.82</v>
+        <v>3.46</v>
       </c>
       <c r="R54" t="n">
-        <v>4.82</v>
+        <v>3.76</v>
       </c>
       <c r="S54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T54" t="n">
         <v>2.15</v>
       </c>
-      <c r="T54" t="n">
-        <v>2.3</v>
-      </c>
       <c r="U54" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="V54" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W54" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X54" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX54" t="n">
         <v>1.35</v>
       </c>
-      <c r="W54" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AY54" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="BA54" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BC54" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BD54" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3.72</v>
+        <v>11.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.58</v>
+        <v>6.6</v>
       </c>
       <c r="R55" t="n">
-        <v>1.98</v>
+        <v>1.2</v>
       </c>
       <c r="S55" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
         <v>1.36</v>
       </c>
-      <c r="W55" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="X55" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF55" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="AG55" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AI55" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN55" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU55" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ55" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BA55" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V56" t="n">
         <v>1.36</v>
       </c>
-      <c r="Q56" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="R56" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="S56" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="T56" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U56" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="V56" t="n">
+      <c r="W56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
         <v>1.28</v>
       </c>
-      <c r="W56" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X56" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC56" t="n">
+      <c r="AQ56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF56" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3568,13 +3568,13 @@
         <v>2.48</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3583,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -3598,40 +3598,40 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3676,13 +3676,13 @@
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.27</v>
+        <v>1.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R28" t="n">
-        <v>2.87</v>
+        <v>3.73</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>3.73</v>
+        <v>2.5</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.28</v>
+        <v>2.31</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.85</v>
+        <v>3.25</v>
       </c>
       <c r="R32" t="n">
-        <v>8.65</v>
+        <v>2.84</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.55</v>
+        <v>1.28</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.6</v>
+        <v>5.85</v>
       </c>
       <c r="R34" t="n">
-        <v>2.5</v>
+        <v>8.65</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.33</v>
+        <v>3.27</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="R40" t="n">
-        <v>2.65</v>
+        <v>1.99</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.27</v>
+        <v>1.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="R43" t="n">
-        <v>1.99</v>
+        <v>4.69</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.82</v>
+        <v>3.46</v>
       </c>
       <c r="R50" t="n">
-        <v>4.82</v>
+        <v>3.76</v>
       </c>
       <c r="S50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T50" t="n">
         <v>2.15</v>
       </c>
-      <c r="T50" t="n">
-        <v>2.3</v>
-      </c>
       <c r="U50" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="V50" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W50" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X50" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX50" t="n">
         <v>1.35</v>
       </c>
-      <c r="W50" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AY50" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="BA50" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BC50" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BD50" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.98</v>
+        <v>3.84</v>
       </c>
       <c r="R51" t="n">
-        <v>8.199999999999999</v>
+        <v>4.36</v>
       </c>
       <c r="S51" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="T51" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U51" t="n">
-        <v>7.1</v>
+        <v>4.33</v>
       </c>
       <c r="V51" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="W51" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="X51" t="n">
-        <v>2.39</v>
+        <v>2.73</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="Z51" t="n">
-        <v>5.55</v>
+        <v>6.9</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AD51" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AI51" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL51" t="n">
         <v>1.95</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AN51" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AU51" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="AV51" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="BA51" t="n">
-        <v>4.75</v>
+        <v>3.65</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="BD51" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,67 +10651,67 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="R52" t="n">
-        <v>4.36</v>
+        <v>4.82</v>
       </c>
       <c r="S52" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T52" t="n">
         <v>2.3</v>
       </c>
-      <c r="T52" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U52" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="V52" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W52" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="X52" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z52" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="AA52" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB52" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB52" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC52" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG52" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI52" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK52" t="n">
         <v>1.75</v>
@@ -10720,64 +10720,64 @@
         <v>1.95</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AN52" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AQ52" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ52" t="n">
         <v>1.38</v>
       </c>
-      <c r="AR52" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>1.35</v>
-      </c>
       <c r="BA52" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC52" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>11.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.46</v>
+        <v>6.6</v>
       </c>
       <c r="R54" t="n">
-        <v>3.76</v>
+        <v>1.2</v>
       </c>
       <c r="S54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF54" t="n">
         <v>3.1</v>
       </c>
-      <c r="AE54" t="n">
+      <c r="AG54" t="n">
         <v>2.05</v>
       </c>
-      <c r="AF54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AH54" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AI54" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN54" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR54" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AT54" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AU54" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AV54" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BA54" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC54" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD54" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>11.5</v>
+        <v>3.72</v>
       </c>
       <c r="Q55" t="n">
-        <v>6.6</v>
+        <v>3.58</v>
       </c>
       <c r="R55" t="n">
-        <v>1.2</v>
+        <v>1.98</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AF55" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL55" t="n">
         <v>2.05</v>
       </c>
-      <c r="AH55" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>0</v>
-      </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BA55" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.72</v>
+        <v>1.36</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.58</v>
+        <v>4.98</v>
       </c>
       <c r="R56" t="n">
-        <v>1.98</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S56" t="n">
-        <v>3.9</v>
+        <v>1.81</v>
       </c>
       <c r="T56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U56" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W56" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF56" t="n">
         <v>2.25</v>
       </c>
-      <c r="U56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="X56" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE56" t="n">
+      <c r="AG56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK56" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF56" t="n">
+      <c r="AL56" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AM56" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN56" t="n">
         <v>3</v>
       </c>
-      <c r="AH56" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AO56" t="n">
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AT56" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AU56" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AV56" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AZ56" t="n">
-        <v>2.8</v>
+        <v>1.23</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.56</v>
+        <v>4.75</v>
       </c>
       <c r="BB56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BF56" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.39</v>
+        <v>3.61</v>
       </c>
       <c r="R2" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.61</v>
+        <v>3.39</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1204,70 +1204,70 @@
         <v>4.57</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1401,70 +1401,70 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1598,70 +1598,70 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.83</v>
+        <v>2.46</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="R11" t="n">
-        <v>2.77</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,22 +3165,22 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3189,10 +3189,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -3204,40 +3204,40 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3282,13 +3282,13 @@
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3583,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -3598,40 +3598,40 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3676,13 +3676,13 @@
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>2.93</v>
+        <v>3.32</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>3.32</v>
+        <v>2.93</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.92</v>
+        <v>2.27</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>3.73</v>
+        <v>2.87</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AF28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AX28" t="n">
         <v>1.91</v>
       </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.31</v>
+        <v>1.28</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.25</v>
+        <v>5.85</v>
       </c>
       <c r="R32" t="n">
-        <v>2.84</v>
+        <v>8.65</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.28</v>
+        <v>2.31</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.85</v>
+        <v>3.25</v>
       </c>
       <c r="R34" t="n">
-        <v>8.65</v>
+        <v>2.84</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.27</v>
+        <v>1.92</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R35" t="n">
-        <v>2.87</v>
+        <v>3.73</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,22 +8090,22 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -8129,28 +8129,28 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK39" t="n">
         <v>0</v>
@@ -8159,10 +8159,10 @@
         <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8207,13 +8207,13 @@
         <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,22 +8287,22 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.27</v>
+        <v>1.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="R40" t="n">
-        <v>1.99</v>
+        <v>4.69</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -8311,10 +8311,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -8326,40 +8326,40 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -8404,13 +8404,13 @@
         <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD40" t="n">
         <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BF40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,22 +8681,22 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.78</v>
+        <v>2.33</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R42" t="n">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8705,10 +8705,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -8720,28 +8720,28 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK42" t="n">
         <v>0</v>
@@ -8750,10 +8750,10 @@
         <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD42" t="n">
         <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BF42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,22 +8878,22 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.6</v>
+        <v>2.78</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="R43" t="n">
-        <v>4.69</v>
+        <v>2.36</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8902,10 +8902,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -8917,40 +8917,40 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8995,13 +8995,13 @@
         <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD43" t="n">
         <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF43" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.46</v>
+        <v>4.98</v>
       </c>
       <c r="R50" t="n">
-        <v>3.76</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S50" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T50" t="n">
         <v>2.5</v>
       </c>
-      <c r="T50" t="n">
-        <v>2.15</v>
-      </c>
       <c r="U50" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W50" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X50" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD50" t="n">
         <v>4.2</v>
       </c>
-      <c r="V50" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W50" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BE50" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,67 +10454,67 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="R51" t="n">
-        <v>4.36</v>
+        <v>4.82</v>
       </c>
       <c r="S51" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T51" t="n">
         <v>2.3</v>
       </c>
-      <c r="T51" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U51" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="V51" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W51" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="X51" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z51" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="AA51" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB51" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB51" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC51" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG51" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI51" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK51" t="n">
         <v>1.75</v>
@@ -10523,64 +10523,64 @@
         <v>1.95</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AN51" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AQ51" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ51" t="n">
         <v>1.38</v>
       </c>
-      <c r="AR51" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>1.35</v>
-      </c>
       <c r="BA51" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC51" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.71</v>
+        <v>3.72</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="R52" t="n">
-        <v>4.82</v>
+        <v>1.98</v>
       </c>
       <c r="S52" t="n">
-        <v>2.15</v>
+        <v>3.9</v>
       </c>
       <c r="T52" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U52" t="n">
-        <v>4.8</v>
+        <v>2.54</v>
       </c>
       <c r="V52" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W52" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="X52" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z52" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AE52" t="n">
         <v>1.8</v>
       </c>
       <c r="AF52" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI52" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AJ52" t="n">
         <v>1.13</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN52" t="n">
-        <v>2.15</v>
+        <v>1.29</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="AW52" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.38</v>
+        <v>2.8</v>
       </c>
       <c r="BA52" t="n">
-        <v>3.5</v>
+        <v>1.56</v>
       </c>
       <c r="BB52" t="n">
         <v>1.22</v>
       </c>
       <c r="BC52" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BE52" t="n">
         <v>1.73</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.34</v>
+        <v>3.84</v>
       </c>
       <c r="R53" t="n">
-        <v>3.66</v>
+        <v>4.36</v>
       </c>
       <c r="S53" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="T53" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U53" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="V53" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="W53" t="n">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
       <c r="X53" t="n">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z53" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="AA53" t="n">
         <v>1.04</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AF53" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK53" t="n">
         <v>1.75</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AL53" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD53" t="n">
         <v>3.6</v>
       </c>
-      <c r="AH53" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB53" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BE53" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>11.5</v>
+        <v>2.08</v>
       </c>
       <c r="Q54" t="n">
-        <v>6.6</v>
+        <v>3.34</v>
       </c>
       <c r="R54" t="n">
-        <v>1.2</v>
+        <v>3.66</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AF54" t="n">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX54" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA54" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB54" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF54" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3.72</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="R55" t="n">
-        <v>1.98</v>
+        <v>3.76</v>
       </c>
       <c r="S55" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="T55" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U55" t="n">
-        <v>2.54</v>
+        <v>4.2</v>
       </c>
       <c r="V55" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W55" t="n">
-        <v>2.89</v>
+        <v>2.69</v>
       </c>
       <c r="X55" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z55" t="n">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC55" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH55" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD55" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AI55" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AL55" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AM55" t="n">
         <v>1.3</v>
       </c>
       <c r="AN55" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB55" t="n">
         <v>1.29</v>
       </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC55" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
         <v>1.36</v>
       </c>
-      <c r="Q56" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="R56" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="S56" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="T56" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U56" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W56" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X56" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AF56" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AG56" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AI56" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL56" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM56" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO56" t="n">
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AT56" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU56" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV56" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BA56" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD56" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>3.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.61</v>
+        <v>3.22</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1598,70 +1598,70 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,70 +1795,70 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1992,70 +1992,70 @@
         <v>2.01</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.78</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="R10" t="n">
-        <v>2.77</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.46</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.43</v>
+        <v>1.93</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>2.46</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2977,70 +2977,70 @@
         <v>5.49</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,22 +3165,22 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3189,10 +3189,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -3204,40 +3204,40 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3282,13 +3282,13 @@
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3780,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3795,40 +3795,40 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,13 +3873,13 @@
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4947,70 +4947,70 @@
         <v>3.32</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5144,70 +5144,70 @@
         <v>2.93</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="Q28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U28" t="n">
         <v>3.5</v>
       </c>
-      <c r="R28" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U28" t="n">
-        <v>3.69</v>
-      </c>
       <c r="V28" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W28" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="X28" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AI28" t="n">
-        <v>4.33</v>
+        <v>5.8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AK28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN28" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="Q30" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="R30" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU30" t="n">
         <v>3.6</v>
       </c>
-      <c r="R30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.18</v>
+        <v>2.27</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>2.33</v>
+        <v>2.87</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.92</v>
+        <v>1.28</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.52</v>
+        <v>5.85</v>
       </c>
       <c r="R35" t="n">
-        <v>3.73</v>
+        <v>8.65</v>
       </c>
       <c r="S35" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.08</v>
+        <v>1.85</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.28</v>
+        <v>1.83</v>
       </c>
       <c r="AI35" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>7.34</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,22 +8090,22 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3.27</v>
+        <v>2.78</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="S39" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T39" t="n">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="U39" t="n">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -8129,40 +8129,40 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.18</v>
+        <v>2.9</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8207,13 +8207,13 @@
         <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,22 +8287,22 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -8311,10 +8311,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -8326,40 +8326,40 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -8404,13 +8404,13 @@
         <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
         <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,22 +8484,22 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -8508,10 +8508,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -8523,28 +8523,28 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK41" t="n">
         <v>0</v>
@@ -8553,10 +8553,10 @@
         <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8601,13 +8601,13 @@
         <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD41" t="n">
         <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BF41" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,22 +8878,22 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.78</v>
+        <v>1.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="R43" t="n">
-        <v>2.36</v>
+        <v>4.69</v>
       </c>
       <c r="S43" t="n">
-        <v>3.2</v>
+        <v>1.98</v>
       </c>
       <c r="T43" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="U43" t="n">
-        <v>2.85</v>
+        <v>4.75</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8902,10 +8902,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -8917,40 +8917,40 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AI43" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AL43" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.32</v>
+        <v>2.12</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8995,13 +8995,13 @@
         <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="BD43" t="n">
         <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="BF43" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="R46" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W46" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="X46" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AT46" t="n">
         <v>2.52</v>
       </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>0</v>
-      </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.84</v>
+        <v>3.68</v>
       </c>
       <c r="R47" t="n">
-        <v>3.58</v>
+        <v>2.52</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.98</v>
+        <v>3.46</v>
       </c>
       <c r="R50" t="n">
-        <v>8.199999999999999</v>
+        <v>3.76</v>
       </c>
       <c r="S50" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="T50" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="U50" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="V50" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="W50" t="n">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="X50" t="n">
-        <v>2.39</v>
+        <v>2.99</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="Z50" t="n">
-        <v>5.55</v>
+        <v>7.9</v>
       </c>
       <c r="AA50" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ50" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE50" t="n">
+      <c r="AK50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ50" t="n">
         <v>1.61</v>
       </c>
-      <c r="AF50" t="n">
+      <c r="BA50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC50" t="n">
         <v>2.25</v>
       </c>
-      <c r="AG50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BD50" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,67 +10454,67 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="R51" t="n">
-        <v>4.82</v>
+        <v>4.36</v>
       </c>
       <c r="S51" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="T51" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U51" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="V51" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W51" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="X51" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z51" t="n">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AF51" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AI51" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK51" t="n">
         <v>1.75</v>
@@ -10523,64 +10523,64 @@
         <v>1.95</v>
       </c>
       <c r="AM51" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB51" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN51" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC51" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.72</v>
+        <v>2.08</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="R52" t="n">
-        <v>1.98</v>
+        <v>3.66</v>
       </c>
       <c r="S52" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="T52" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U52" t="n">
-        <v>2.54</v>
+        <v>4</v>
       </c>
       <c r="V52" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W52" t="n">
-        <v>2.89</v>
+        <v>2.59</v>
       </c>
       <c r="X52" t="n">
-        <v>2.73</v>
+        <v>2.94</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z52" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AA52" t="n">
         <v>1.04</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC52" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH52" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD52" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE52" t="n">
+      <c r="AI52" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK52" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF52" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AL52" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AM52" t="n">
         <v>1.3</v>
       </c>
       <c r="AN52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB52" t="n">
         <v>1.29</v>
       </c>
-      <c r="AO52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC52" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,67 +10848,67 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="R53" t="n">
-        <v>4.36</v>
+        <v>4.82</v>
       </c>
       <c r="S53" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T53" t="n">
         <v>2.3</v>
       </c>
-      <c r="T53" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U53" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="V53" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W53" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="X53" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z53" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="AA53" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB53" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB53" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC53" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG53" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI53" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK53" t="n">
         <v>1.75</v>
@@ -10917,64 +10917,64 @@
         <v>1.95</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AN53" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AQ53" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ53" t="n">
         <v>1.38</v>
       </c>
-      <c r="AR53" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>1.35</v>
-      </c>
       <c r="BA53" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC53" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BD53" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.08</v>
+        <v>11.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.34</v>
+        <v>6.6</v>
       </c>
       <c r="R54" t="n">
-        <v>3.66</v>
+        <v>1.2</v>
       </c>
       <c r="S54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF54" t="n">
         <v>3.1</v>
       </c>
-      <c r="AE54" t="n">
+      <c r="AG54" t="n">
         <v>2.05</v>
       </c>
-      <c r="AF54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AH54" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AI54" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU54" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BA54" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC54" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD54" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.46</v>
+        <v>4.98</v>
       </c>
       <c r="R55" t="n">
-        <v>3.76</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S55" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T55" t="n">
         <v>2.5</v>
       </c>
-      <c r="T55" t="n">
-        <v>2.15</v>
-      </c>
       <c r="U55" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X55" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD55" t="n">
         <v>4.2</v>
       </c>
-      <c r="V55" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W55" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X55" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BE55" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>11.5</v>
+        <v>3.72</v>
       </c>
       <c r="Q56" t="n">
-        <v>6.6</v>
+        <v>3.58</v>
       </c>
       <c r="R56" t="n">
-        <v>1.2</v>
+        <v>1.98</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AF56" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL56" t="n">
         <v>2.05</v>
       </c>
-      <c r="AH56" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>0</v>
-      </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN56" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO56" t="n">
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR56" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS56" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW56" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX56" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY56" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ56" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BA56" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BB56" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD56" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE56" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF56" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.18</v>
+        <v>2.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.22</v>
+        <v>3.39</v>
       </c>
       <c r="R2" t="n">
-        <v>2.33</v>
+        <v>2.84</v>
       </c>
       <c r="S2" t="n">
-        <v>3.88</v>
+        <v>2.99</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>2.99</v>
+        <v>3.62</v>
       </c>
       <c r="V2" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="X2" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="Y2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC2" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AD2" t="n">
-        <v>3.19</v>
+        <v>2.74</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.01</v>
+        <v>2.27</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.58</v>
+        <v>3.89</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.36</v>
+        <v>3.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.39</v>
+        <v>3.22</v>
       </c>
       <c r="R3" t="n">
-        <v>2.84</v>
+        <v>2.33</v>
       </c>
       <c r="S3" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U3" t="n">
         <v>2.99</v>
       </c>
-      <c r="T3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3.62</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AS3" t="n">
         <v>2.59</v>
       </c>
-      <c r="X3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,70 +1401,70 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1598,70 +1598,70 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,124 +1795,124 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="T7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="X7" t="n">
         <v>2.5</v>
       </c>
-      <c r="U7" t="n">
+      <c r="Y7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL7" t="n">
         <v>2.15</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AM7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.15</v>
-      </c>
       <c r="BC7" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.83</v>
+        <v>2.46</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="R11" t="n">
-        <v>2.77</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.46</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.43</v>
+        <v>1.93</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3780,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3795,40 +3795,40 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,13 +3873,13 @@
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,22 +4150,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4174,10 +4174,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -4189,40 +4189,40 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,13 +4267,13 @@
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.31</v>
+        <v>3.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>3.67</v>
       </c>
       <c r="R28" t="n">
-        <v>2.84</v>
+        <v>2.33</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>4.05</v>
       </c>
       <c r="T28" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="U28" t="n">
-        <v>3.5</v>
+        <v>2.36</v>
       </c>
       <c r="V28" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W28" t="n">
-        <v>2.7</v>
+        <v>3.52</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.15</v>
+        <v>4.48</v>
       </c>
       <c r="AE28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC28" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF28" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.07</v>
-      </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="Q29" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU29" t="n">
         <v>3.6</v>
       </c>
-      <c r="R29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>3.73</v>
+        <v>2.84</v>
       </c>
       <c r="S30" t="n">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="T30" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="U30" t="n">
-        <v>4.56</v>
+        <v>3.5</v>
       </c>
       <c r="V30" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W30" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="X30" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>1.28</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AH30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM30" t="n">
         <v>1.28</v>
       </c>
-      <c r="AI30" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AN30" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,55 +6908,55 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.18</v>
+        <v>2.27</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>2.33</v>
+        <v>2.87</v>
       </c>
       <c r="S33" t="n">
-        <v>4.05</v>
+        <v>2.6</v>
       </c>
       <c r="T33" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U33" t="n">
-        <v>2.36</v>
+        <v>3.69</v>
       </c>
       <c r="V33" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W33" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="X33" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="AA33" t="n">
         <v>1.09</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>4.48</v>
+        <v>4.2</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AG33" t="n">
         <v>2.6</v>
@@ -6965,76 +6965,76 @@
         <v>1.44</v>
       </c>
       <c r="AI33" t="n">
-        <v>4.58</v>
+        <v>4.33</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AM33" t="n">
         <v>1.27</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.28</v>
+        <v>2.55</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.85</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>8.65</v>
+        <v>2.5</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7353,10 +7353,10 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,22 +8090,22 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.78</v>
+        <v>1.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="R39" t="n">
-        <v>2.36</v>
+        <v>4.69</v>
       </c>
       <c r="S39" t="n">
-        <v>3.2</v>
+        <v>1.98</v>
       </c>
       <c r="T39" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="U39" t="n">
-        <v>2.85</v>
+        <v>4.75</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -8129,40 +8129,40 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AI39" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.32</v>
+        <v>2.12</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8207,13 +8207,13 @@
         <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,22 +8287,22 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -8311,10 +8311,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -8326,28 +8326,28 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
@@ -8356,10 +8356,10 @@
         <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -8404,13 +8404,13 @@
         <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD40" t="n">
         <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BF40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,22 +8484,22 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.27</v>
+        <v>2.78</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="R41" t="n">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="S41" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T41" t="n">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="U41" t="n">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -8508,10 +8508,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -8523,40 +8523,40 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.18</v>
+        <v>2.9</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AI41" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8601,13 +8601,13 @@
         <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="BD41" t="n">
         <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="BF41" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,22 +8878,22 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8902,10 +8902,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -8917,40 +8917,40 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8995,13 +8995,13 @@
         <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
         <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS48" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AT48" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BA48" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2</v>
+        <v>11.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.46</v>
+        <v>6.6</v>
       </c>
       <c r="R50" t="n">
-        <v>3.76</v>
+        <v>1.2</v>
       </c>
       <c r="S50" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF50" t="n">
         <v>3.1</v>
       </c>
-      <c r="AE50" t="n">
+      <c r="AG50" t="n">
         <v>2.05</v>
       </c>
-      <c r="AF50" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AH50" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AI50" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN50" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR50" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AS50" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AT50" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AU50" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BA50" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC50" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,67 +10454,67 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="R51" t="n">
-        <v>4.36</v>
+        <v>4.82</v>
       </c>
       <c r="S51" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T51" t="n">
         <v>2.3</v>
       </c>
-      <c r="T51" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U51" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="V51" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W51" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="X51" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z51" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="AA51" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB51" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB51" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC51" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG51" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI51" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK51" t="n">
         <v>1.75</v>
@@ -10523,64 +10523,64 @@
         <v>1.95</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AN51" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AQ51" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ51" t="n">
         <v>1.38</v>
       </c>
-      <c r="AR51" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>1.35</v>
-      </c>
       <c r="BA51" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC51" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.08</v>
+        <v>3.72</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="R52" t="n">
-        <v>3.66</v>
+        <v>1.98</v>
       </c>
       <c r="S52" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="T52" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U52" t="n">
-        <v>4</v>
+        <v>2.54</v>
       </c>
       <c r="V52" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W52" t="n">
-        <v>2.59</v>
+        <v>2.89</v>
       </c>
       <c r="X52" t="n">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z52" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AA52" t="n">
         <v>1.04</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH52" t="n">
         <v>1.33</v>
       </c>
-      <c r="AD52" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE52" t="n">
+      <c r="AI52" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL52" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>1.91</v>
       </c>
       <c r="AM52" t="n">
         <v>1.3</v>
       </c>
       <c r="AN52" t="n">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="BA52" t="n">
-        <v>2.8</v>
+        <v>1.56</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BC52" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.82</v>
+        <v>4.98</v>
       </c>
       <c r="R53" t="n">
-        <v>4.82</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S53" t="n">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="T53" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="U53" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="V53" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W53" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="X53" t="n">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="Z53" t="n">
-        <v>6.4</v>
+        <v>5.55</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AE53" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK53" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1.75</v>
       </c>
       <c r="AL53" t="n">
         <v>1.95</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AN53" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ53" t="n">
         <v>1.23</v>
       </c>
-      <c r="AQ53" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>1.38</v>
-      </c>
       <c r="BA53" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="BB53" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BF53" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE53" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF53" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>11.5</v>
+        <v>2.08</v>
       </c>
       <c r="Q54" t="n">
-        <v>6.6</v>
+        <v>3.34</v>
       </c>
       <c r="R54" t="n">
-        <v>1.2</v>
+        <v>3.66</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AF54" t="n">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX54" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA54" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB54" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF54" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.98</v>
+        <v>3.84</v>
       </c>
       <c r="R55" t="n">
-        <v>8.199999999999999</v>
+        <v>4.36</v>
       </c>
       <c r="S55" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="T55" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U55" t="n">
-        <v>7.1</v>
+        <v>4.33</v>
       </c>
       <c r="V55" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="W55" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="X55" t="n">
-        <v>2.39</v>
+        <v>2.73</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="Z55" t="n">
-        <v>5.55</v>
+        <v>6.9</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AD55" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AI55" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL55" t="n">
         <v>1.95</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AN55" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="AT55" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AU55" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="BA55" t="n">
-        <v>4.75</v>
+        <v>3.65</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BC55" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.72</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="R56" t="n">
-        <v>1.98</v>
+        <v>3.76</v>
       </c>
       <c r="S56" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="T56" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U56" t="n">
-        <v>2.54</v>
+        <v>4.2</v>
       </c>
       <c r="V56" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W56" t="n">
-        <v>2.89</v>
+        <v>2.69</v>
       </c>
       <c r="X56" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z56" t="n">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH56" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD56" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AI56" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AL56" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AM56" t="n">
         <v>1.3</v>
       </c>
       <c r="AN56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB56" t="n">
         <v>1.29</v>
       </c>
-      <c r="AO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC56" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="BD56" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,70 +1401,70 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,70 +1795,70 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.85</v>
+        <v>3.23</v>
       </c>
       <c r="R10" t="n">
-        <v>2.77</v>
+        <v>3.31</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.46</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.43</v>
+        <v>1.93</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>2.46</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>2.48</v>
       </c>
       <c r="S16" t="n">
-        <v>4.94</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="V16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>1.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
         <v>3.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.85</v>
+        <v>5.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,22 +4150,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4174,10 +4174,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -4189,40 +4189,40 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,13 +4267,13 @@
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,67 +4938,67 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>3.32</v>
+        <v>2.93</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="U23" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="V23" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W23" t="n">
-        <v>3.12</v>
+        <v>2.91</v>
       </c>
       <c r="X23" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AB23" t="n">
         <v>1.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" t="n">
-        <v>4.55</v>
+        <v>5.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK23" t="n">
         <v>1.62</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,67 +5135,67 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R24" t="n">
-        <v>2.93</v>
+        <v>3.32</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="U24" t="n">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W24" t="n">
-        <v>2.91</v>
+        <v>3.12</v>
       </c>
       <c r="X24" t="n">
-        <v>2.53</v>
+        <v>2.36</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AB24" t="n">
         <v>1.04</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.5</v>
+        <v>4.55</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK24" t="n">
         <v>1.62</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,55 +5923,55 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.18</v>
+        <v>2.27</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>2.33</v>
+        <v>2.87</v>
       </c>
       <c r="S28" t="n">
-        <v>4.05</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U28" t="n">
-        <v>2.36</v>
+        <v>3.69</v>
       </c>
       <c r="V28" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W28" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="X28" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="AA28" t="n">
         <v>1.09</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.48</v>
+        <v>4.2</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AG28" t="n">
         <v>2.6</v>
@@ -5980,76 +5980,76 @@
         <v>1.44</v>
       </c>
       <c r="AI28" t="n">
-        <v>4.58</v>
+        <v>4.33</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AM28" t="n">
         <v>1.27</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>3.73</v>
+        <v>2.84</v>
       </c>
       <c r="S29" t="n">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="T29" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="U29" t="n">
-        <v>4.56</v>
+        <v>3.5</v>
       </c>
       <c r="V29" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W29" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="X29" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>1.28</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AI29" t="n">
-        <v>5.95</v>
+        <v>5.8</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AL29" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.31</v>
+        <v>3.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>3.67</v>
       </c>
       <c r="R30" t="n">
-        <v>2.84</v>
+        <v>2.33</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>4.05</v>
       </c>
       <c r="T30" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="U30" t="n">
-        <v>3.5</v>
+        <v>2.36</v>
       </c>
       <c r="V30" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W30" t="n">
-        <v>2.7</v>
+        <v>3.52</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.15</v>
+        <v>4.48</v>
       </c>
       <c r="AE30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC30" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF30" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>2.07</v>
-      </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.27</v>
+        <v>1.92</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R33" t="n">
-        <v>2.87</v>
+        <v>3.73</v>
       </c>
       <c r="S33" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="T33" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="U33" t="n">
-        <v>3.69</v>
+        <v>4.56</v>
       </c>
       <c r="V33" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W33" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="X33" t="n">
-        <v>2.39</v>
+        <v>2.77</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.3</v>
+        <v>6.75</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AD33" t="n">
-        <v>4.2</v>
+        <v>3.28</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AI33" t="n">
-        <v>4.33</v>
+        <v>5.95</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AM33" t="n">
         <v>1.27</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AS33" t="n">
         <v>2.05</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="AU33" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AY33" t="n">
         <v>1.38</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.37</v>
+        <v>2.85</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.33</v>
+        <v>3.78</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W37" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y37" t="n">
         <v>1.45</v>
       </c>
-      <c r="Q37" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U37" t="n">
-        <v>8</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.56</v>
-      </c>
       <c r="Z37" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AB37" t="n">
         <v>1.03</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AD37" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AE37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX37" t="n">
         <v>1.57</v>
       </c>
-      <c r="AF37" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ37" t="n">
+      <c r="AY37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BB37" t="n">
         <v>1.2</v>
       </c>
-      <c r="AK37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC37" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,22 +8090,22 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.6</v>
+        <v>2.78</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>4.69</v>
+        <v>2.36</v>
       </c>
       <c r="S39" t="n">
-        <v>1.98</v>
+        <v>3.2</v>
       </c>
       <c r="T39" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="U39" t="n">
-        <v>4.75</v>
+        <v>2.85</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -8129,40 +8129,40 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AN39" t="n">
-        <v>2.12</v>
+        <v>1.32</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8207,13 +8207,13 @@
         <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,22 +8287,22 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.27</v>
+        <v>1.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="R40" t="n">
-        <v>1.99</v>
+        <v>4.69</v>
       </c>
       <c r="S40" t="n">
-        <v>3.35</v>
+        <v>1.98</v>
       </c>
       <c r="T40" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="U40" t="n">
-        <v>2.43</v>
+        <v>4.75</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -8311,7 +8311,7 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="Y40" t="n">
         <v>1.58</v>
@@ -8329,37 +8329,37 @@
         <v>1.13</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AF40" t="n">
         <v>2.38</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AI40" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AJ40" t="n">
         <v>1.21</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -8404,13 +8404,13 @@
         <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="BD40" t="n">
         <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="BF40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,22 +8484,22 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.78</v>
+        <v>3.27</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="R41" t="n">
-        <v>2.36</v>
+        <v>1.99</v>
       </c>
       <c r="S41" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T41" t="n">
-        <v>2.23</v>
+        <v>2.48</v>
       </c>
       <c r="U41" t="n">
-        <v>2.85</v>
+        <v>2.43</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -8508,10 +8508,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -8523,40 +8523,40 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AI41" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8601,13 +8601,13 @@
         <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="BD41" t="n">
         <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="BF41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,22 +8681,22 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8705,10 +8705,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -8720,28 +8720,28 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
         <v>0</v>
@@ -8750,10 +8750,10 @@
         <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
         <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,22 +8878,22 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8902,10 +8902,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -8917,28 +8917,28 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK43" t="n">
         <v>0</v>
@@ -8947,10 +8947,10 @@
         <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8995,13 +8995,13 @@
         <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD43" t="n">
         <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BF43" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>11.5</v>
+        <v>1.77</v>
       </c>
       <c r="Q50" t="n">
-        <v>6.6</v>
+        <v>3.84</v>
       </c>
       <c r="R50" t="n">
-        <v>1.2</v>
+        <v>4.36</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AF50" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="AH50" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX50" t="n">
         <v>1.68</v>
       </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>0</v>
-      </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.82</v>
+        <v>3.34</v>
       </c>
       <c r="R51" t="n">
-        <v>4.82</v>
+        <v>3.66</v>
       </c>
       <c r="S51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T51" t="n">
         <v>2.15</v>
       </c>
-      <c r="T51" t="n">
-        <v>2.3</v>
-      </c>
       <c r="U51" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="V51" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W51" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X51" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y51" t="n">
         <v>1.35</v>
       </c>
-      <c r="W51" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X51" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.43</v>
-      </c>
       <c r="Z51" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AA51" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB51" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB51" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AC51" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="AE51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK51" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK51" t="n">
+      <c r="AL51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN51" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL51" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM51" t="n">
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN51" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AQ51" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AU51" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AV51" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="BA51" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BC51" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.98</v>
+        <v>3.46</v>
       </c>
       <c r="R53" t="n">
-        <v>8.199999999999999</v>
+        <v>3.76</v>
       </c>
       <c r="S53" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="T53" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="U53" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="V53" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="W53" t="n">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="X53" t="n">
-        <v>2.39</v>
+        <v>2.99</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="Z53" t="n">
-        <v>5.55</v>
+        <v>7.9</v>
       </c>
       <c r="AA53" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ53" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE53" t="n">
+      <c r="AK53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ53" t="n">
         <v>1.61</v>
       </c>
-      <c r="AF53" t="n">
+      <c r="BA53" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC53" t="n">
         <v>2.25</v>
       </c>
-      <c r="AG53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB53" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BD53" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.34</v>
+        <v>4.98</v>
       </c>
       <c r="R54" t="n">
-        <v>3.66</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S54" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T54" t="n">
         <v>2.5</v>
       </c>
-      <c r="T54" t="n">
-        <v>2.15</v>
-      </c>
       <c r="U54" t="n">
-        <v>4</v>
+        <v>7.1</v>
       </c>
       <c r="V54" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W54" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X54" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH54" t="n">
         <v>1.44</v>
       </c>
-      <c r="W54" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI54" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AK54" t="n">
         <v>1.8</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AN54" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.45</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AT54" t="n">
         <v>2.75</v>
       </c>
       <c r="AU54" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AV54" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AY54" t="n">
         <v>1.37</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="BA54" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BC54" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="BD54" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.77</v>
+        <v>11.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.84</v>
+        <v>6.6</v>
       </c>
       <c r="R55" t="n">
-        <v>4.36</v>
+        <v>1.2</v>
       </c>
       <c r="S55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="AG55" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AI55" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AT55" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU55" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BA55" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R56" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W56" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF56" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="R56" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T56" t="n">
+      <c r="AG56" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN56" t="n">
         <v>2.15</v>
       </c>
-      <c r="U56" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V56" t="n">
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ56" t="n">
         <v>1.41</v>
       </c>
-      <c r="W56" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X56" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN56" t="n">
+      <c r="AR56" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE56" t="n">
         <v>1.73</v>
       </c>
-      <c r="AO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BF56" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,70 +1401,70 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1613,7 +1613,7 @@
         <v>3.84</v>
       </c>
       <c r="X6" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="Y6" t="n">
         <v>1.62</v>
@@ -1628,7 +1628,7 @@
         <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AD6" t="n">
         <v>5.15</v>
@@ -1640,7 +1640,7 @@
         <v>2.46</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AH6" t="n">
         <v>1.62</v>
@@ -1649,7 +1649,7 @@
         <v>3.58</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
         <v>1.46</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BC6" t="n">
         <v>1.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,70 +1795,70 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3386,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -3401,40 +3401,40 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3479,13 +3479,13 @@
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3583,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -3598,40 +3598,40 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3676,13 +3676,13 @@
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4553,70 +4553,70 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4661,13 +4661,13 @@
         <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,67 +4938,67 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>2.93</v>
+        <v>3.32</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="U23" t="n">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="V23" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W23" t="n">
-        <v>2.91</v>
+        <v>3.12</v>
       </c>
       <c r="X23" t="n">
-        <v>2.53</v>
+        <v>2.36</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AB23" t="n">
         <v>1.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.5</v>
+        <v>4.55</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK23" t="n">
         <v>1.62</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,67 +5135,67 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>3.32</v>
+        <v>2.93</v>
       </c>
       <c r="S24" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="U24" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="V24" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>3.12</v>
+        <v>2.91</v>
       </c>
       <c r="X24" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AB24" t="n">
         <v>1.04</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.55</v>
+        <v>5.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK24" t="n">
         <v>1.62</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5735,124 +5735,124 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="Q28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U28" t="n">
         <v>3.5</v>
       </c>
-      <c r="R28" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U28" t="n">
-        <v>3.69</v>
-      </c>
       <c r="V28" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W28" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="X28" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AI28" t="n">
-        <v>4.33</v>
+        <v>5.8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AK28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN28" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,76 +6120,76 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R29" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="S29" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="T29" t="n">
-        <v>2.16</v>
+        <v>2.43</v>
       </c>
       <c r="U29" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="V29" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W29" t="n">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AI29" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AN29" t="n">
         <v>1.5</v>
@@ -6198,55 +6198,55 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3.18</v>
+        <v>1.22</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.67</v>
+        <v>5.7</v>
       </c>
       <c r="R30" t="n">
-        <v>2.33</v>
+        <v>7.9</v>
       </c>
       <c r="S30" t="n">
-        <v>4.05</v>
+        <v>1.62</v>
       </c>
       <c r="T30" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
-        <v>2.36</v>
+        <v>7</v>
       </c>
       <c r="V30" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="W30" t="n">
-        <v>3.52</v>
+        <v>4.15</v>
       </c>
       <c r="X30" t="n">
-        <v>2.43</v>
+        <v>1.97</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AB30" t="n">
         <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AD30" t="n">
-        <v>4.48</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.33</v>
+        <v>2.89</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.44</v>
+        <v>1.86</v>
       </c>
       <c r="AI30" t="n">
-        <v>4.58</v>
+        <v>3.1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6398,52 +6398,52 @@
         <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AU30" t="n">
         <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU31" t="n">
         <v>3.6</v>
       </c>
-      <c r="R31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.28</v>
+        <v>2.27</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.85</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>8.65</v>
+        <v>2.87</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ32" t="n">
         <v>1.85</v>
       </c>
-      <c r="AH32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4.1</v>
+        <v>1.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="R37" t="n">
-        <v>1.76</v>
+        <v>7.34</v>
       </c>
       <c r="S37" t="n">
-        <v>4.33</v>
+        <v>1.61</v>
       </c>
       <c r="T37" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="U37" t="n">
-        <v>2.25</v>
+        <v>8</v>
       </c>
       <c r="V37" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W37" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="X37" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AB37" t="n">
         <v>1.03</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AH37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ37" t="n">
         <v>1.36</v>
       </c>
-      <c r="AI37" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM37" t="n">
+      <c r="AR37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF37" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W38" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1.45</v>
       </c>
-      <c r="Q38" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U38" t="n">
-        <v>8</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.56</v>
-      </c>
       <c r="Z38" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AB38" t="n">
         <v>1.03</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AE38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX38" t="n">
         <v>1.57</v>
       </c>
-      <c r="AF38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ38" t="n">
+      <c r="AY38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BB38" t="n">
         <v>1.2</v>
       </c>
-      <c r="AK38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC38" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,22 +8287,22 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -8311,10 +8311,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -8326,40 +8326,40 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -8404,13 +8404,13 @@
         <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
         <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,22 +8484,22 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.27</v>
+        <v>2.33</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="R41" t="n">
-        <v>1.99</v>
+        <v>2.65</v>
       </c>
       <c r="S41" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="T41" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="U41" t="n">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -8526,19 +8526,19 @@
         <v>1.13</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AI41" t="n">
         <v>3.65</v>
@@ -8553,10 +8553,10 @@
         <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8601,13 +8601,13 @@
         <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="BD41" t="n">
         <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="BF41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,22 +8681,22 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8705,10 +8705,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -8720,28 +8720,28 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK42" t="n">
         <v>0</v>
@@ -8750,10 +8750,10 @@
         <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD42" t="n">
         <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BF42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,22 +8878,22 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.33</v>
+        <v>1.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="R43" t="n">
-        <v>2.65</v>
+        <v>4.69</v>
       </c>
       <c r="S43" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="T43" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="U43" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="Y43" t="n">
         <v>1.58</v>
@@ -8920,37 +8920,37 @@
         <v>1.13</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AI43" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AJ43" t="n">
         <v>1.21</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8995,13 +8995,13 @@
         <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BD43" t="n">
         <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="BF43" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.26</v>
+        <v>1.91</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="R48" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS49" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU49" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BA49" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.84</v>
+        <v>4.98</v>
       </c>
       <c r="R50" t="n">
-        <v>4.36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S50" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="T50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U50" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W50" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X50" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF50" t="n">
         <v>2.25</v>
       </c>
-      <c r="U50" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W50" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AG50" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI50" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL50" t="n">
         <v>1.95</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AN50" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="AS50" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AU50" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="AV50" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="AW50" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="BA50" t="n">
-        <v>3.65</v>
+        <v>4.75</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC50" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="BD50" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.08</v>
+        <v>3.72</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="R51" t="n">
-        <v>3.66</v>
+        <v>1.98</v>
       </c>
       <c r="S51" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="T51" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U51" t="n">
-        <v>4</v>
+        <v>2.54</v>
       </c>
       <c r="V51" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W51" t="n">
-        <v>2.59</v>
+        <v>2.89</v>
       </c>
       <c r="X51" t="n">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z51" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AA51" t="n">
         <v>1.04</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH51" t="n">
         <v>1.33</v>
       </c>
-      <c r="AD51" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE51" t="n">
+      <c r="AI51" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL51" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>1.91</v>
       </c>
       <c r="AM51" t="n">
         <v>1.3</v>
       </c>
       <c r="AN51" t="n">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AU51" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AV51" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="BA51" t="n">
-        <v>2.8</v>
+        <v>1.56</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BC51" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="R52" t="n">
-        <v>1.98</v>
+        <v>4.82</v>
       </c>
       <c r="S52" t="n">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
       <c r="T52" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U52" t="n">
-        <v>2.54</v>
+        <v>4.8</v>
       </c>
       <c r="V52" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W52" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="X52" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z52" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AA52" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB52" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB52" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC52" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AE52" t="n">
         <v>1.8</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG52" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI52" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AJ52" t="n">
         <v>1.13</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL52" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN52" t="n">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AT52" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AZ52" t="n">
-        <v>2.8</v>
+        <v>1.38</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.56</v>
+        <v>3.5</v>
       </c>
       <c r="BB52" t="n">
         <v>1.22</v>
       </c>
       <c r="BC52" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE52" t="n">
         <v>1.73</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.46</v>
+        <v>3.34</v>
       </c>
       <c r="R53" t="n">
-        <v>3.76</v>
+        <v>3.66</v>
       </c>
       <c r="S53" t="n">
         <v>2.5</v>
@@ -10863,25 +10863,25 @@
         <v>2.15</v>
       </c>
       <c r="U53" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="V53" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W53" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="X53" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z53" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB53" t="n">
         <v>1.06</v>
@@ -10911,55 +10911,55 @@
         <v>1.08</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL53" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AM53" t="n">
         <v>1.3</v>
       </c>
       <c r="AN53" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="AR53" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="AT53" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="AU53" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="AV53" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="BA53" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="BB53" t="n">
         <v>1.29</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
         <v>1.36</v>
       </c>
-      <c r="Q54" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="R54" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="S54" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U54" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W54" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AF54" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AI54" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU54" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV54" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BA54" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD54" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>11.5</v>
+        <v>1.77</v>
       </c>
       <c r="Q55" t="n">
-        <v>6.6</v>
+        <v>3.84</v>
       </c>
       <c r="R55" t="n">
-        <v>1.2</v>
+        <v>4.36</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AF55" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="AH55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX55" t="n">
         <v>1.68</v>
       </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>0</v>
-      </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BA55" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.82</v>
+        <v>3.46</v>
       </c>
       <c r="R56" t="n">
-        <v>4.82</v>
+        <v>3.76</v>
       </c>
       <c r="S56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T56" t="n">
         <v>2.15</v>
       </c>
-      <c r="T56" t="n">
-        <v>2.3</v>
-      </c>
       <c r="U56" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="V56" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W56" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX56" t="n">
         <v>1.35</v>
       </c>
-      <c r="W56" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X56" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AY56" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="BA56" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BC56" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BD56" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="R58" t="n">
-        <v>4.2</v>
+        <v>4.07</v>
       </c>
       <c r="S58" t="n">
         <v>2.7</v>
@@ -11851,25 +11851,25 @@
         <v>5</v>
       </c>
       <c r="V58" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="W58" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="X58" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="Y58" t="n">
         <v>1.15</v>
       </c>
       <c r="Z58" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA58" t="n">
         <v>1.02</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AC58" t="n">
         <v>1.7</v>
@@ -11878,13 +11878,13 @@
         <v>2.05</v>
       </c>
       <c r="AE58" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AF58" t="n">
         <v>1.33</v>
       </c>
       <c r="AG58" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AH58" t="n">
         <v>1.08</v>
@@ -11896,7 +11896,7 @@
         <v>1.02</v>
       </c>
       <c r="AK58" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AL58" t="n">
         <v>1.44</v>
@@ -11911,40 +11911,40 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR58" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AS58" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU58" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AV58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW58" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX58" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY58" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ58" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BA58" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BB58" t="n">
         <v>1.5</v>
@@ -11959,7 +11959,7 @@
         <v>1.3</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="BG58" t="n">
         <v>0</v>
@@ -12030,34 +12030,34 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="R59" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="S59" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="T59" t="n">
         <v>1.85</v>
       </c>
       <c r="U59" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="V59" t="n">
         <v>1.63</v>
       </c>
       <c r="W59" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="X59" t="n">
         <v>3.96</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z59" t="n">
         <v>13</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,79 +12424,79 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI61" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK61" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM61" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN61" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO61" t="n">
         <v>0</v>
@@ -12505,52 +12505,52 @@
         <v>0</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR61" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AS61" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AU61" t="n">
         <v>0</v>
       </c>
       <c r="AV61" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AW61" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AX61" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AY61" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AZ61" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA61" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BB61" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE61" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF61" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG61" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="R2" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="S2" t="n">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
@@ -840,7 +840,7 @@
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AD2" t="n">
         <v>2.74</v>
@@ -849,13 +849,13 @@
         <v>2.27</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG2" t="n">
         <v>3.89</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AI2" t="n">
         <v>8.699999999999999</v>
@@ -870,7 +870,7 @@
         <v>1.81</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AN2" t="n">
         <v>1.57</v>
@@ -882,10 +882,10 @@
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
@@ -897,10 +897,10 @@
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -998,28 +998,28 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="R3" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="S3" t="n">
         <v>3.88</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="U3" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="V3" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="X3" t="n">
         <v>3.08</v>
@@ -1028,43 +1028,43 @@
         <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
         <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.7</v>
+        <v>6.71</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AM3" t="n">
         <v>1.38</v>
@@ -1115,13 +1115,13 @@
         <v>1.27</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="BD3" t="n">
         <v>3.45</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="BF3" t="n">
         <v>1.14</v>
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.43</v>
+        <v>3.26</v>
       </c>
       <c r="R4" t="n">
-        <v>4.57</v>
+        <v>4.15</v>
       </c>
       <c r="S4" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="X4" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AA4" t="n">
         <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.26</v>
+        <v>3.98</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AM4" t="n">
         <v>1.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1276,13 +1276,13 @@
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
@@ -1291,13 +1291,13 @@
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.91</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="S8" t="n">
         <v>4.1</v>
@@ -2034,7 +2034,7 @@
         <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="AH8" t="n">
         <v>1.32</v>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="R11" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="S11" t="n">
         <v>3.5</v>
@@ -2616,7 +2616,7 @@
         <v>1.52</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="AE11" t="n">
         <v>2.46</v>
@@ -2625,7 +2625,7 @@
         <v>1.43</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.7</v>
+        <v>5.21</v>
       </c>
       <c r="AH11" t="n">
         <v>1.12</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
@@ -2670,10 +2670,10 @@
         <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
@@ -2968,16 +2968,16 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.02</v>
+        <v>3.85</v>
       </c>
       <c r="R13" t="n">
-        <v>5.49</v>
+        <v>5.9</v>
       </c>
       <c r="S13" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="T13" t="n">
         <v>2.23</v>
@@ -3016,13 +3016,13 @@
         <v>2.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
         <v>3.42</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AI13" t="n">
         <v>6.55</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
         <v>4.94</v>
@@ -3774,10 +3774,10 @@
         <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="X17" t="n">
         <v>2.73</v>
@@ -3786,7 +3786,7 @@
         <v>1.39</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="AA17" t="n">
         <v>1.05</v>
@@ -3801,19 +3801,19 @@
         <v>3.5</v>
       </c>
       <c r="AE17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF17" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AH17" t="n">
         <v>1.28</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.85</v>
+        <v>5.9</v>
       </c>
       <c r="AJ17" t="n">
         <v>1.11</v>
@@ -3825,16 +3825,16 @@
         <v>1.8</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.52</v>
@@ -3849,7 +3849,7 @@
         <v>3.35</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="AV17" t="n">
         <v>2.3</v>
@@ -3858,7 +3858,7 @@
         <v>1.82</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AY17" t="n">
         <v>1.3</v>
@@ -3879,10 +3879,10 @@
         <v>3.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4553,70 +4553,70 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4661,13 +4661,13 @@
         <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4750,70 +4750,70 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4858,13 +4858,13 @@
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF22" t="n">
         <v>0</v>
@@ -4938,67 +4938,67 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="S23" t="n">
         <v>2.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="U23" t="n">
         <v>3.8</v>
       </c>
       <c r="V23" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="X23" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC23" t="n">
         <v>1.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AE23" t="n">
         <v>1.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK23" t="n">
         <v>1.62</v>
@@ -5055,13 +5055,13 @@
         <v>1.16</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="BD23" t="n">
         <v>4.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="BF23" t="n">
         <v>1.23</v>
@@ -5135,28 +5135,28 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="T24" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="U24" t="n">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="V24" t="n">
         <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="X24" t="n">
         <v>2.53</v>
@@ -5168,31 +5168,31 @@
         <v>6.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.5</v>
+        <v>5.49</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.13</v>
@@ -5207,7 +5207,7 @@
         <v>1.3</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,16 +5249,16 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="BF24" t="n">
         <v>1.19</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X32" t="n">
         <v>2.27</v>
       </c>
-      <c r="Q32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.39</v>
-      </c>
       <c r="Y32" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="AH32" t="n">
         <v>1.44</v>
       </c>
       <c r="AI32" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN32" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL32" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN32" t="n">
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR32" t="n">
         <v>1.6</v>
       </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AS32" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="AU32" t="n">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.78</v>
+        <v>2.57</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.37</v>
+        <v>1.78</v>
       </c>
       <c r="BB32" t="n">
         <v>1.18</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="R35" t="n">
-        <v>2.33</v>
+        <v>1.82</v>
       </c>
       <c r="S35" t="n">
         <v>4.05</v>
@@ -7341,7 +7341,7 @@
         <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AD35" t="n">
         <v>4.48</v>
@@ -7368,13 +7368,13 @@
         <v>1.58</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AM35" t="n">
         <v>1.27</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W37" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y37" t="n">
         <v>1.45</v>
       </c>
-      <c r="Q37" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U37" t="n">
-        <v>8</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.56</v>
-      </c>
       <c r="Z37" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AB37" t="n">
         <v>1.03</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AD37" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AE37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX37" t="n">
         <v>1.57</v>
       </c>
-      <c r="AF37" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ37" t="n">
+      <c r="AY37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BB37" t="n">
         <v>1.2</v>
       </c>
-      <c r="AK37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC37" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,22 +8090,22 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.78</v>
+        <v>2.33</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R39" t="n">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="S39" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="T39" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="U39" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -8129,40 +8129,40 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.45</v>
+        <v>4.75</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.9</v>
+        <v>2.17</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AI39" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8207,13 +8207,13 @@
         <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,22 +8287,22 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -8311,10 +8311,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -8326,40 +8326,40 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -8404,13 +8404,13 @@
         <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD40" t="n">
         <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BF40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,22 +8484,22 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.33</v>
+        <v>3.27</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="R41" t="n">
-        <v>2.65</v>
+        <v>1.99</v>
       </c>
       <c r="S41" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="T41" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U41" t="n">
         <v>2.43</v>
-      </c>
-      <c r="U41" t="n">
-        <v>2.9</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -8526,19 +8526,19 @@
         <v>1.13</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AI41" t="n">
         <v>3.65</v>
@@ -8553,10 +8553,10 @@
         <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.21</v>
+        <v>1.64</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8601,13 +8601,13 @@
         <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="BD41" t="n">
         <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="BF41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,22 +8681,22 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.27</v>
+        <v>2.78</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="R42" t="n">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="S42" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T42" t="n">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="U42" t="n">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8705,10 +8705,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -8720,40 +8720,40 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.18</v>
+        <v>2.9</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AI42" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="BD42" t="n">
         <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="BF42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,22 +8878,22 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8902,10 +8902,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -8917,40 +8917,40 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8995,13 +8995,13 @@
         <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
         <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
         <v>0</v>
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.47</v>
+        <v>3.27</v>
       </c>
       <c r="R44" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="R45" t="n">
-        <v>6.24</v>
+        <v>6.4</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9469,28 +9469,28 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="S46" t="n">
         <v>2.38</v>
       </c>
       <c r="T46" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="U46" t="n">
         <v>4.1</v>
       </c>
       <c r="V46" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W46" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="X46" t="n">
         <v>2.6</v>
@@ -9499,10 +9499,10 @@
         <v>1.49</v>
       </c>
       <c r="Z46" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AB46" t="n">
         <v>1.04</v>
@@ -9511,7 +9511,7 @@
         <v>1.22</v>
       </c>
       <c r="AD46" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AE46" t="n">
         <v>1.72</v>
@@ -9529,7 +9529,7 @@
         <v>5.25</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AK46" t="n">
         <v>1.65</v>
@@ -9538,10 +9538,10 @@
         <v>2.2</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9553,10 +9553,10 @@
         <v>1.35</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AT46" t="n">
         <v>2.52</v>
@@ -9565,10 +9565,10 @@
         <v>4.03</v>
       </c>
       <c r="AV46" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AX46" t="n">
         <v>1.74</v>
@@ -9577,19 +9577,19 @@
         <v>1.46</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BA46" t="n">
         <v>2.82</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="BD46" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE46" t="n">
         <v>1.83</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AT47" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU47" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BA47" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R50" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W50" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X50" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH50" t="n">
         <v>1.36</v>
       </c>
-      <c r="Q50" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="R50" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="S50" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U50" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W50" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AI50" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL50" t="n">
         <v>1.95</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AN50" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AS50" t="n">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AU50" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BA50" t="n">
         <v>3.35</v>
       </c>
-      <c r="AV50" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>4.75</v>
-      </c>
       <c r="BB50" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF50" t="n">
         <v>1.2</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,37 +10454,37 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.72</v>
+        <v>1.66</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="R51" t="n">
-        <v>1.98</v>
+        <v>4.1</v>
       </c>
       <c r="S51" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="T51" t="n">
         <v>2.25</v>
       </c>
       <c r="U51" t="n">
-        <v>2.54</v>
+        <v>4.8</v>
       </c>
       <c r="V51" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W51" t="n">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="X51" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z51" t="n">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
       <c r="AA51" t="n">
         <v>1.04</v>
@@ -10496,91 +10496,91 @@
         <v>1.25</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG51" t="n">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="AH51" t="n">
         <v>1.33</v>
       </c>
       <c r="AI51" t="n">
-        <v>5.75</v>
+        <v>6.26</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL51" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN51" t="n">
         <v>2.05</v>
       </c>
-      <c r="AM51" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="AT51" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="AU51" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="AV51" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.84</v>
+        <v>2.07</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AZ51" t="n">
-        <v>2.8</v>
+        <v>1.35</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.56</v>
+        <v>3.65</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC51" t="n">
         <v>2.05</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.71</v>
+        <v>9.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.82</v>
+        <v>6</v>
       </c>
       <c r="R52" t="n">
-        <v>4.82</v>
+        <v>1.28</v>
       </c>
       <c r="S52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AF52" t="n">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AI52" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW52" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BA52" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD52" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="R53" t="n">
-        <v>3.66</v>
+        <v>3.35</v>
       </c>
       <c r="S53" t="n">
         <v>2.5</v>
@@ -10899,7 +10899,7 @@
         <v>1.75</v>
       </c>
       <c r="AG53" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="AH53" t="n">
         <v>1.25</v>
@@ -10917,46 +10917,46 @@
         <v>1.91</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN53" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AU53" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AV53" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="BA53" t="n">
         <v>2.8</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>11.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="R54" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AF54" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="AG54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL54" t="n">
         <v>2.05</v>
       </c>
-      <c r="AH54" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>0</v>
-      </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN54" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS54" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU54" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV54" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW54" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX54" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BA54" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BB54" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD54" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE54" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF54" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="R55" t="n">
-        <v>4.36</v>
+        <v>3.8</v>
       </c>
       <c r="S55" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="T55" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U55" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="V55" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W55" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="X55" t="n">
-        <v>2.73</v>
+        <v>2.94</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z55" t="n">
-        <v>6.9</v>
+        <v>7.7</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB55" t="n">
         <v>1.05</v>
       </c>
       <c r="AC55" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH55" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD55" t="n">
+      <c r="AI55" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD55" t="n">
         <v>3.5</v>
       </c>
-      <c r="AE55" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BE55" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.46</v>
+        <v>4.6</v>
       </c>
       <c r="R56" t="n">
-        <v>3.76</v>
+        <v>7</v>
       </c>
       <c r="S56" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="T56" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="U56" t="n">
+        <v>6</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W56" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD56" t="n">
         <v>4.2</v>
       </c>
-      <c r="V56" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W56" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X56" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BE56" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.33</v>
+        <v>3.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="R2" t="n">
-        <v>2.81</v>
+        <v>2.22</v>
       </c>
       <c r="S2" t="n">
-        <v>3.11</v>
+        <v>3.88</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="U2" t="n">
-        <v>3.62</v>
+        <v>3.02</v>
       </c>
       <c r="V2" t="n">
         <v>1.43</v>
       </c>
       <c r="W2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AS2" t="n">
         <v>2.59</v>
       </c>
-      <c r="X2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.19</v>
+        <v>2.33</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.17</v>
+        <v>3.36</v>
       </c>
       <c r="R3" t="n">
-        <v>2.22</v>
+        <v>2.81</v>
       </c>
       <c r="S3" t="n">
-        <v>3.88</v>
+        <v>3.11</v>
       </c>
       <c r="T3" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>3.02</v>
+        <v>3.62</v>
       </c>
       <c r="V3" t="n">
         <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="X3" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.13</v>
+        <v>2.74</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.09</v>
+        <v>2.27</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.65</v>
+        <v>3.89</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.71</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.32</v>
+        <v>2.61</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,70 +1401,70 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1476,13 +1476,13 @@
         <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
@@ -1491,13 +1491,13 @@
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1598,70 +1598,70 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1795,13 +1795,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U7" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V7" t="n">
         <v>1.35</v>
@@ -1816,49 +1816,49 @@
         <v>1.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AA7" t="n">
         <v>1.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AE7" t="n">
         <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AG7" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1870,10 +1870,10 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT7" t="n">
         <v>0</v>
@@ -1885,10 +1885,10 @@
         <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3386,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -3401,40 +3401,40 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3479,13 +3479,13 @@
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="S17" t="n">
-        <v>4.94</v>
+        <v>3.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>1.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AM17" t="n">
         <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,28 +5923,28 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -5962,40 +5962,40 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6040,13 +6040,13 @@
         <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.22</v>
+        <v>2.31</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.7</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>7.9</v>
+        <v>2.84</v>
       </c>
       <c r="S30" t="n">
-        <v>1.62</v>
+        <v>2.8</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="U30" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="V30" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="W30" t="n">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="X30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.32</v>
+        <v>1.91</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.89</v>
+        <v>1.74</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.01</v>
+        <v>3.2</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.86</v>
+        <v>1.27</v>
       </c>
       <c r="AI30" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AN30" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6398,52 +6398,52 @@
         <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
         <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.55</v>
+        <v>2.07</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.3</v>
+        <v>1.58</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6595,52 +6595,52 @@
         <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AU31" t="n">
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,55 +7105,55 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.08</v>
+        <v>3.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="R34" t="n">
-        <v>2.8</v>
+        <v>1.82</v>
       </c>
       <c r="S34" t="n">
-        <v>2.6</v>
+        <v>4.05</v>
       </c>
       <c r="T34" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U34" t="n">
-        <v>3.3</v>
+        <v>2.36</v>
       </c>
       <c r="V34" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W34" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="X34" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="AA34" t="n">
         <v>1.09</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC34" t="n">
         <v>1.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.2</v>
+        <v>4.48</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AG34" t="n">
         <v>2.6</v>
@@ -7162,76 +7162,76 @@
         <v>1.44</v>
       </c>
       <c r="AI34" t="n">
-        <v>4.33</v>
+        <v>4.58</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AM34" t="n">
         <v>1.27</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC34" t="n">
         <v>1.91</v>
       </c>
-      <c r="AY34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>1.85</v>
-      </c>
       <c r="BD34" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,55 +7302,55 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.75</v>
+        <v>2.08</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="R35" t="n">
-        <v>1.82</v>
+        <v>2.8</v>
       </c>
       <c r="S35" t="n">
-        <v>4.05</v>
+        <v>2.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U35" t="n">
-        <v>2.36</v>
+        <v>3.3</v>
       </c>
       <c r="V35" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W35" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="X35" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="AA35" t="n">
         <v>1.09</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC35" t="n">
         <v>1.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.48</v>
+        <v>4.2</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AG35" t="n">
         <v>2.6</v>
@@ -7359,76 +7359,76 @@
         <v>1.44</v>
       </c>
       <c r="AI35" t="n">
-        <v>4.58</v>
+        <v>4.33</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AM35" t="n">
         <v>1.27</v>
       </c>
       <c r="AN35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
         <v>1.17</v>
       </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.46</v>
+        <v>4.11</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.98</v>
+        <v>3.84</v>
       </c>
       <c r="R36" t="n">
-        <v>8.6</v>
+        <v>1.75</v>
       </c>
       <c r="S36" t="n">
-        <v>1.61</v>
+        <v>4.33</v>
       </c>
       <c r="T36" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="U36" t="n">
-        <v>8</v>
+        <v>2.25</v>
       </c>
       <c r="V36" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W36" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="X36" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AB36" t="n">
         <v>1.03</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AI36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ36" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BB36" t="n">
         <v>1.2</v>
       </c>
-      <c r="AK36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC36" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,22 +8090,22 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.33</v>
+        <v>1.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="R39" t="n">
-        <v>2.65</v>
+        <v>4.69</v>
       </c>
       <c r="S39" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="T39" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="U39" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="Y39" t="n">
         <v>1.58</v>
@@ -8132,37 +8132,37 @@
         <v>1.13</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AJ39" t="n">
         <v>1.21</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8207,13 +8207,13 @@
         <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,22 +8287,22 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.6</v>
+        <v>2.33</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="R40" t="n">
-        <v>4.69</v>
+        <v>2.65</v>
       </c>
       <c r="S40" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="T40" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="U40" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -8311,7 +8311,7 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="Y40" t="n">
         <v>1.58</v>
@@ -8329,37 +8329,37 @@
         <v>1.13</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AI40" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AJ40" t="n">
         <v>1.21</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AN40" t="n">
-        <v>2.12</v>
+        <v>1.43</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -8404,13 +8404,13 @@
         <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BD40" t="n">
         <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="BF40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,22 +8484,22 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -8508,10 +8508,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -8523,28 +8523,28 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
         <v>0</v>
@@ -8553,10 +8553,10 @@
         <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8601,13 +8601,13 @@
         <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
         <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,22 +8681,22 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.78</v>
+        <v>3.27</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="R42" t="n">
-        <v>2.36</v>
+        <v>1.99</v>
       </c>
       <c r="S42" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T42" t="n">
-        <v>2.23</v>
+        <v>2.48</v>
       </c>
       <c r="U42" t="n">
-        <v>2.85</v>
+        <v>2.43</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8705,10 +8705,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -8720,40 +8720,40 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AI42" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="BD42" t="n">
         <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="BF42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,22 +8878,22 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8902,10 +8902,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -8917,40 +8917,40 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8995,13 +8995,13 @@
         <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD43" t="n">
         <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF43" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S46" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T46" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="U46" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="V46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W46" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="X46" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY46" t="n">
         <v>1.3</v>
       </c>
-      <c r="W46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X46" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ46" t="n">
+      <c r="AZ46" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BF46" t="n">
         <v>1.35</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.91</v>
+        <v>2.37</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R48" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W48" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="X48" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG48" t="n">
         <v>3</v>
       </c>
-      <c r="S48" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U48" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="V48" t="n">
+      <c r="AH48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF48" t="n">
         <v>1.2</v>
-      </c>
-      <c r="W48" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BF48" t="n">
-        <v>1.35</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,79 +10060,79 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.37</v>
+        <v>1.84</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R49" t="n">
-        <v>2.84</v>
+        <v>4</v>
       </c>
       <c r="S49" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="T49" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="U49" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="V49" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="W49" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="X49" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="Z49" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AB49" t="n">
         <v>1.04</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AD49" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG49" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AI49" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL49" t="n">
         <v>2.2</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN49" t="n">
-        <v>1.57</v>
+        <v>1.99</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -10141,52 +10141,52 @@
         <v>1.18</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AS49" t="n">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AU49" t="n">
-        <v>3.92</v>
+        <v>4.03</v>
       </c>
       <c r="AV49" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="AW49" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BA49" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BC49" t="n">
         <v>2</v>
       </c>
       <c r="BD49" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="R50" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="S50" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="T50" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="U50" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="V50" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W50" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X50" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y50" t="n">
         <v>1.35</v>
       </c>
-      <c r="W50" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.43</v>
-      </c>
       <c r="Z50" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AA50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB50" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB50" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AC50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD50" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE50" t="n">
+      <c r="AQ50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR50" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF50" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AS50" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="AT50" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AU50" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="AV50" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="BA50" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BC50" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BD50" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.66</v>
+        <v>9.5</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="R51" t="n">
-        <v>4.1</v>
+        <v>1.28</v>
       </c>
       <c r="S51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.91</v>
+        <v>2.87</v>
       </c>
       <c r="AG51" t="n">
-        <v>3.26</v>
+        <v>2.05</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AI51" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN51" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU51" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AW51" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BA51" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC51" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD51" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>9.5</v>
+        <v>1.43</v>
       </c>
       <c r="Q52" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U52" t="n">
         <v>6</v>
       </c>
-      <c r="R52" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.87</v>
+        <v>2.2</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.05</v>
+        <v>2.68</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.68</v>
+        <v>1.41</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS52" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU52" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV52" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX52" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY52" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BA52" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BB52" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD52" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="R53" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W53" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X53" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BA53" t="n">
         <v>3.35</v>
       </c>
-      <c r="S53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T53" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U53" t="n">
-        <v>4</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W53" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X53" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP53" t="n">
+      <c r="BB53" t="n">
         <v>1.22</v>
       </c>
-      <c r="AQ53" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB53" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC53" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BD53" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,37 +11045,37 @@
         </is>
       </c>
       <c r="P54" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q54" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q54" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R54" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="S54" t="n">
-        <v>3.95</v>
+        <v>2.3</v>
       </c>
       <c r="T54" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U54" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="V54" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W54" t="n">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="X54" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Z54" t="n">
-        <v>6.5</v>
+        <v>6.95</v>
       </c>
       <c r="AA54" t="n">
         <v>1.04</v>
@@ -11087,91 +11087,91 @@
         <v>1.25</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF54" t="n">
         <v>1.91</v>
       </c>
       <c r="AG54" t="n">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="AH54" t="n">
         <v>1.33</v>
       </c>
       <c r="AI54" t="n">
-        <v>5.85</v>
+        <v>6.26</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL54" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN54" t="n">
         <v>2.05</v>
       </c>
-      <c r="AM54" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="AT54" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="AU54" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="AV54" t="n">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AZ54" t="n">
-        <v>2.63</v>
+        <v>1.35</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.62</v>
+        <v>3.65</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BC54" t="n">
         <v>2.05</v>
       </c>
       <c r="BD54" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="Q55" t="n">
         <v>3.5</v>
       </c>
       <c r="R55" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="S55" t="n">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="T55" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U55" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="V55" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W55" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="X55" t="n">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="Z55" t="n">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB55" t="n">
         <v>1.05</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
       <c r="AE55" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AG55" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AI55" t="n">
-        <v>6.5</v>
+        <v>5.85</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AM55" t="n">
         <v>1.3</v>
       </c>
       <c r="AN55" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AQ55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BE55" t="n">
         <v>1.72</v>
       </c>
-      <c r="AR55" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>1.62</v>
-      </c>
       <c r="BF55" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.43</v>
+        <v>1.95</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="R56" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="S56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W56" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK56" t="n">
         <v>1.85</v>
       </c>
-      <c r="T56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U56" t="n">
-        <v>6</v>
-      </c>
-      <c r="V56" t="n">
+      <c r="AL56" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM56" t="n">
         <v>1.3</v>
       </c>
-      <c r="W56" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="X56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE56" t="n">
+      <c r="AN56" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE56" t="n">
         <v>1.62</v>
       </c>
-      <c r="AF56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BF56" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.19</v>
+        <v>2.33</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.17</v>
+        <v>3.36</v>
       </c>
       <c r="R2" t="n">
-        <v>2.22</v>
+        <v>2.81</v>
       </c>
       <c r="S2" t="n">
-        <v>3.88</v>
+        <v>3.11</v>
       </c>
       <c r="T2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>3.02</v>
+        <v>3.62</v>
       </c>
       <c r="V2" t="n">
         <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="X2" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.13</v>
+        <v>2.74</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.09</v>
+        <v>2.27</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.65</v>
+        <v>3.89</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.71</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.32</v>
+        <v>2.61</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.33</v>
+        <v>3.19</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="R3" t="n">
-        <v>2.81</v>
+        <v>2.22</v>
       </c>
       <c r="S3" t="n">
-        <v>3.11</v>
+        <v>3.88</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="U3" t="n">
-        <v>3.62</v>
+        <v>3.02</v>
       </c>
       <c r="V3" t="n">
         <v>1.43</v>
       </c>
       <c r="W3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AS3" t="n">
         <v>2.59</v>
       </c>
-      <c r="X3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,70 +1401,70 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1476,13 +1476,13 @@
         <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
@@ -1491,13 +1491,13 @@
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1598,124 +1598,124 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,124 +1795,124 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>2.79</v>
+        <v>3.84</v>
       </c>
       <c r="X7" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>1.27</v>
       </c>
-      <c r="AD7" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
       <c r="AR7" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
         <v>3.23</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4553,70 +4553,70 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4661,13 +4661,13 @@
         <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4750,70 +4750,70 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4858,13 +4858,13 @@
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,67 +4938,67 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD23" t="n">
         <v>3.5</v>
       </c>
-      <c r="R23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" t="n">
-        <v>4.35</v>
+        <v>5.49</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK23" t="n">
         <v>1.62</v>
@@ -5010,7 +5010,7 @@
         <v>1.3</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,67 +5135,67 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="S24" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="U24" t="n">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W24" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="X24" t="n">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG24" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.49</v>
+        <v>4.35</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK24" t="n">
         <v>1.62</v>
@@ -5207,7 +5207,7 @@
         <v>1.3</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="BD24" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.31</v>
+        <v>3.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="R30" t="n">
-        <v>2.84</v>
+        <v>1.82</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>4.05</v>
       </c>
       <c r="T30" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="U30" t="n">
-        <v>3.5</v>
+        <v>2.36</v>
       </c>
       <c r="V30" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W30" t="n">
-        <v>2.7</v>
+        <v>3.52</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.15</v>
+        <v>4.48</v>
       </c>
       <c r="AE30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC30" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF30" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>2.07</v>
-      </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.22</v>
+        <v>2.31</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.7</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>7.9</v>
+        <v>2.84</v>
       </c>
       <c r="S31" t="n">
-        <v>1.62</v>
+        <v>2.8</v>
       </c>
       <c r="T31" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="U31" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="W31" t="n">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="X31" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AD31" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.32</v>
+        <v>1.91</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.89</v>
+        <v>1.74</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.01</v>
+        <v>3.2</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.86</v>
+        <v>1.27</v>
       </c>
       <c r="AI31" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AN31" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6595,52 +6595,52 @@
         <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.55</v>
+        <v>2.07</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>2.3</v>
+        <v>1.58</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.13</v>
+        <v>1.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.42</v>
+        <v>5.7</v>
       </c>
       <c r="R32" t="n">
-        <v>2.68</v>
+        <v>7.9</v>
       </c>
       <c r="S32" t="n">
-        <v>2.73</v>
+        <v>1.62</v>
       </c>
       <c r="T32" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="V32" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="W32" t="n">
-        <v>3.28</v>
+        <v>4.15</v>
       </c>
       <c r="X32" t="n">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BC32" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ32" t="n">
+      <c r="BD32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BF32" t="n">
         <v>1.42</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="R35" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="S35" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="T35" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="U35" t="n">
         <v>3.3</v>
       </c>
       <c r="V35" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W35" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="X35" t="n">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="AH35" t="n">
         <v>1.44</v>
       </c>
       <c r="AI35" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AN35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR35" t="n">
         <v>1.6</v>
       </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AS35" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="AU35" t="n">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.78</v>
+        <v>2.57</v>
       </c>
       <c r="AW35" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.37</v>
+        <v>1.78</v>
       </c>
       <c r="BB35" t="n">
         <v>1.18</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.46</v>
+        <v>4.11</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.98</v>
+        <v>3.84</v>
       </c>
       <c r="R38" t="n">
-        <v>8.6</v>
+        <v>1.75</v>
       </c>
       <c r="S38" t="n">
-        <v>1.61</v>
+        <v>4.33</v>
       </c>
       <c r="T38" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="U38" t="n">
-        <v>8</v>
+        <v>2.25</v>
       </c>
       <c r="V38" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W38" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="X38" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AB38" t="n">
         <v>1.03</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AI38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BB38" t="n">
         <v>1.2</v>
       </c>
-      <c r="AK38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC38" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,22 +8287,22 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -8311,10 +8311,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -8326,28 +8326,28 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
@@ -8356,10 +8356,10 @@
         <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -8404,13 +8404,13 @@
         <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
         <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,22 +8484,22 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -8508,10 +8508,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -8523,28 +8523,28 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK41" t="n">
         <v>0</v>
@@ -8553,10 +8553,10 @@
         <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8601,13 +8601,13 @@
         <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD41" t="n">
         <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BF41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,22 +8681,22 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.27</v>
+        <v>2.78</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="R42" t="n">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="S42" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T42" t="n">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="U42" t="n">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8705,10 +8705,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -8720,40 +8720,40 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.18</v>
+        <v>2.9</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AI42" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="BD42" t="n">
         <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="BF42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,22 +8878,22 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.78</v>
+        <v>3.27</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="R43" t="n">
-        <v>2.36</v>
+        <v>1.99</v>
       </c>
       <c r="S43" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T43" t="n">
-        <v>2.23</v>
+        <v>2.48</v>
       </c>
       <c r="U43" t="n">
-        <v>2.85</v>
+        <v>2.43</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8902,10 +8902,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -8917,40 +8917,40 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AI43" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8995,13 +8995,13 @@
         <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="BD43" t="n">
         <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="BF43" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AU46" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S49" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T49" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="U49" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="V49" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W49" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="X49" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY49" t="n">
         <v>1.3</v>
       </c>
-      <c r="W49" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ49" t="n">
+      <c r="AZ49" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BF49" t="n">
         <v>1.35</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R50" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="S50" t="n">
         <v>2.5</v>
@@ -10272,13 +10272,13 @@
         <v>2.15</v>
       </c>
       <c r="U50" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="V50" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W50" t="n">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="X50" t="n">
         <v>2.94</v>
@@ -10287,100 +10287,100 @@
         <v>1.35</v>
       </c>
       <c r="Z50" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AD50" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="AE50" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG50" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AH50" t="n">
         <v>1.25</v>
       </c>
       <c r="AI50" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL50" t="n">
         <v>1.91</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AN50" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB50" t="n">
         <v>1.22</v>
       </c>
-      <c r="AQ50" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC50" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BD50" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BF50" t="n">
         <v>1.15</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>9.5</v>
+        <v>2.04</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="R51" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U51" t="n">
+        <v>4</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W51" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X51" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM51" t="n">
         <v>1.28</v>
       </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
+      <c r="AN51" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ51" t="n">
         <v>1.4</v>
       </c>
-      <c r="AF51" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0</v>
-      </c>
       <c r="AR51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU51" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY51" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA51" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB51" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF51" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.43</v>
+        <v>9.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="R52" t="n">
-        <v>7</v>
+        <v>1.28</v>
       </c>
       <c r="S52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.2</v>
+        <v>2.87</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.68</v>
+        <v>2.05</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.41</v>
+        <v>1.68</v>
       </c>
       <c r="AI52" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BA52" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD52" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="R53" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="S53" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="T53" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U53" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="V53" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W53" t="n">
-        <v>2.94</v>
+        <v>3.22</v>
       </c>
       <c r="X53" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="Z53" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB53" t="n">
         <v>1.04</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AD53" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AE53" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK53" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1.75</v>
       </c>
       <c r="AL53" t="n">
         <v>1.95</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AN53" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="AT53" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AU53" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="AV53" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="AW53" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE53" t="n">
         <v>1.8</v>
       </c>
-      <c r="AX53" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BB53" t="n">
+      <c r="BF53" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE53" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF53" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,67 +11045,67 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="R54" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="S54" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="T54" t="n">
         <v>2.3</v>
       </c>
-      <c r="T54" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U54" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="V54" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W54" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="X54" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="Z54" t="n">
-        <v>6.95</v>
+        <v>6.25</v>
       </c>
       <c r="AA54" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB54" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB54" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC54" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG54" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI54" t="n">
-        <v>6.26</v>
+        <v>5.5</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK54" t="n">
         <v>1.75</v>
@@ -11117,61 +11117,61 @@
         <v>1.25</v>
       </c>
       <c r="AN54" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="AU54" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="AV54" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AW54" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="BA54" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC54" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BD54" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,37 +11242,37 @@
         </is>
       </c>
       <c r="P55" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q55" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q55" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R55" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="S55" t="n">
-        <v>3.95</v>
+        <v>2.3</v>
       </c>
       <c r="T55" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U55" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="V55" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W55" t="n">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="X55" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Z55" t="n">
-        <v>6.5</v>
+        <v>6.95</v>
       </c>
       <c r="AA55" t="n">
         <v>1.04</v>
@@ -11284,91 +11284,91 @@
         <v>1.25</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF55" t="n">
         <v>1.91</v>
       </c>
       <c r="AG55" t="n">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="AH55" t="n">
         <v>1.33</v>
       </c>
       <c r="AI55" t="n">
-        <v>5.85</v>
+        <v>6.26</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL55" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN55" t="n">
         <v>2.05</v>
       </c>
-      <c r="AM55" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="AT55" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="AU55" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AZ55" t="n">
-        <v>2.63</v>
+        <v>1.35</v>
       </c>
       <c r="BA55" t="n">
-        <v>1.62</v>
+        <v>3.65</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BC55" t="n">
         <v>2.05</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="Q56" t="n">
         <v>3.5</v>
       </c>
       <c r="R56" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="S56" t="n">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="T56" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U56" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="V56" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W56" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="X56" t="n">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="Z56" t="n">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB56" t="n">
         <v>1.05</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
       <c r="AE56" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AG56" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AI56" t="n">
-        <v>6.5</v>
+        <v>5.85</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AL56" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AM56" t="n">
         <v>1.3</v>
       </c>
       <c r="AN56" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="AO56" t="n">
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AQ56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BE56" t="n">
         <v>1.72</v>
       </c>
-      <c r="AR56" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>1.62</v>
-      </c>
       <c r="BF56" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>

--- a/jogos_2026-05-11.xlsx
+++ b/jogos_2026-05-11.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.33</v>
+        <v>3.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="R2" t="n">
-        <v>2.81</v>
+        <v>2.22</v>
       </c>
       <c r="S2" t="n">
-        <v>3.11</v>
+        <v>3.88</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="U2" t="n">
-        <v>3.62</v>
+        <v>3.02</v>
       </c>
       <c r="V2" t="n">
         <v>1.43</v>
       </c>
       <c r="W2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AS2" t="n">
         <v>2.59</v>
       </c>
-      <c r="X2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.19</v>
+        <v>2.33</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.17</v>
+        <v>3.36</v>
       </c>
       <c r="R3" t="n">
-        <v>2.22</v>
+        <v>2.81</v>
       </c>
       <c r="S3" t="n">
-        <v>3.88</v>
+        <v>2.99</v>
       </c>
       <c r="T3" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>3.02</v>
+        <v>3.62</v>
       </c>
       <c r="V3" t="n">
         <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="X3" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.13</v>
+        <v>2.74</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.09</v>
+        <v>2.27</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.65</v>
+        <v>3.89</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.71</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,22 +1195,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.26</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>4.15</v>
+        <v>3.47</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="T4" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="V4" t="n">
         <v>1.44</v>
@@ -1219,109 +1219,109 @@
         <v>2.66</v>
       </c>
       <c r="X4" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="Y4" t="n">
         <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AK4" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.47</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.28</v>
+        <v>3.36</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,124 +1401,124 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1598,124 +1598,124 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.23</v>
+        <v>2.82</v>
       </c>
       <c r="R10" t="n">
-        <v>3.31</v>
+        <v>2.74</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="V1